--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4088400</v>
+        <v>4435100</v>
       </c>
       <c r="E8" s="3">
-        <v>4905000</v>
+        <v>4240400</v>
       </c>
       <c r="F8" s="3">
-        <v>4438900</v>
+        <v>5087300</v>
       </c>
       <c r="G8" s="3">
-        <v>4031100</v>
+        <v>4603900</v>
       </c>
       <c r="H8" s="3">
-        <v>4796600</v>
+        <v>4181000</v>
       </c>
       <c r="I8" s="3">
-        <v>5926000</v>
+        <v>4974900</v>
       </c>
       <c r="J8" s="3">
+        <v>6146300</v>
+      </c>
+      <c r="K8" s="3">
         <v>4263500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4367500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3452900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3250600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3169900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1249900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2787400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2567200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3202000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3928000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4515500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4529900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4254800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4330700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4068100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4220300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2789600</v>
+        <v>2811000</v>
       </c>
       <c r="E9" s="3">
-        <v>2936700</v>
+        <v>2893300</v>
       </c>
       <c r="F9" s="3">
-        <v>2862200</v>
+        <v>3045900</v>
       </c>
       <c r="G9" s="3">
-        <v>2639300</v>
+        <v>2968600</v>
       </c>
       <c r="H9" s="3">
-        <v>3139400</v>
+        <v>2737400</v>
       </c>
       <c r="I9" s="3">
-        <v>3386900</v>
+        <v>3256100</v>
       </c>
       <c r="J9" s="3">
+        <v>3512800</v>
+      </c>
+      <c r="K9" s="3">
         <v>2667000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2333100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2229300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1995300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1897500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>625800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1676100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1603700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1894400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2471300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2899500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2997100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2845600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2839000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2625700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2710500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1298800</v>
+        <v>1624100</v>
       </c>
       <c r="E10" s="3">
-        <v>1968300</v>
+        <v>1347100</v>
       </c>
       <c r="F10" s="3">
-        <v>1576700</v>
+        <v>2041500</v>
       </c>
       <c r="G10" s="3">
-        <v>1391800</v>
+        <v>1635300</v>
       </c>
       <c r="H10" s="3">
-        <v>1657300</v>
+        <v>1443600</v>
       </c>
       <c r="I10" s="3">
-        <v>2539100</v>
+        <v>1718900</v>
       </c>
       <c r="J10" s="3">
+        <v>2633500</v>
+      </c>
+      <c r="K10" s="3">
         <v>1596500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2034400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1223600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1255300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1272400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>624100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1111300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>963600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1307600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1456800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1616100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1532800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1409100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1491700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1442300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1509700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>929900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>969000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,61 +1298,64 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>419700</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-300</v>
       </c>
-      <c r="G14" s="3">
-        <v>26200</v>
-      </c>
       <c r="H14" s="3">
-        <v>4500</v>
+        <v>27200</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>27700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>185300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100900</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1353,11 +1372,11 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1374,100 +1393,106 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>212800</v>
+        <v>240800</v>
       </c>
       <c r="E15" s="3">
-        <v>214000</v>
+        <v>220700</v>
       </c>
       <c r="F15" s="3">
-        <v>200200</v>
+        <v>222000</v>
       </c>
       <c r="G15" s="3">
         <v>207600</v>
       </c>
       <c r="H15" s="3">
-        <v>195400</v>
+        <v>215300</v>
       </c>
       <c r="I15" s="3">
-        <v>198200</v>
+        <v>202600</v>
       </c>
       <c r="J15" s="3">
+        <v>205600</v>
+      </c>
+      <c r="K15" s="3">
         <v>184700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>199100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>196400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>177300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>174000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>88100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>173300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>184400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>192100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>236000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>269100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>243400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>237500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>193900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>189400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>193400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>207100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>228100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>167900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>160800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>166700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>197200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4118000</v>
+        <v>4649200</v>
       </c>
       <c r="E17" s="3">
-        <v>4178900</v>
+        <v>4271100</v>
       </c>
       <c r="F17" s="3">
-        <v>4051800</v>
+        <v>4334200</v>
       </c>
       <c r="G17" s="3">
-        <v>3902600</v>
+        <v>4202400</v>
       </c>
       <c r="H17" s="3">
-        <v>4095100</v>
+        <v>4047700</v>
       </c>
       <c r="I17" s="3">
-        <v>4515800</v>
+        <v>4247400</v>
       </c>
       <c r="J17" s="3">
+        <v>4683700</v>
+      </c>
+      <c r="K17" s="3">
         <v>3694400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3418800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3214700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2965200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2948300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>535800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2595600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2728100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2976300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3972200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4488800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4454100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4252500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4310600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3857600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3914800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-29500</v>
+        <v>-214100</v>
       </c>
       <c r="E18" s="3">
-        <v>726100</v>
+        <v>-30600</v>
       </c>
       <c r="F18" s="3">
-        <v>387200</v>
+        <v>753100</v>
       </c>
       <c r="G18" s="3">
-        <v>128500</v>
+        <v>401500</v>
       </c>
       <c r="H18" s="3">
-        <v>701500</v>
+        <v>133300</v>
       </c>
       <c r="I18" s="3">
-        <v>1410100</v>
+        <v>727600</v>
       </c>
       <c r="J18" s="3">
+        <v>1462600</v>
+      </c>
+      <c r="K18" s="3">
         <v>569100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>948700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>238300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>285400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>221500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>714100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>191800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-160900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>225700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-44200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>75900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>210400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>305500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>358100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>522300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>269000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>341100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>297200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>242200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>81100</v>
+        <v>31700</v>
       </c>
       <c r="E20" s="3">
-        <v>-43500</v>
+        <v>84100</v>
       </c>
       <c r="F20" s="3">
-        <v>-158800</v>
+        <v>-45200</v>
       </c>
       <c r="G20" s="3">
-        <v>52600</v>
+        <v>-164700</v>
       </c>
       <c r="H20" s="3">
-        <v>70000</v>
+        <v>54500</v>
       </c>
       <c r="I20" s="3">
-        <v>-92800</v>
+        <v>72600</v>
       </c>
       <c r="J20" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="K20" s="3">
         <v>221000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>83700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-62000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>54000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>65600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>184400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-152000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>62700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-426500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>52700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-170700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-51800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>20800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-51000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-30000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>60900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>27100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>264400</v>
+        <v>478000</v>
       </c>
       <c r="E21" s="3">
-        <v>896600</v>
+        <v>274200</v>
       </c>
       <c r="F21" s="3">
-        <v>428300</v>
+        <v>929900</v>
       </c>
       <c r="G21" s="3">
-        <v>414900</v>
+        <v>444200</v>
       </c>
       <c r="H21" s="3">
-        <v>971300</v>
+        <v>430300</v>
       </c>
       <c r="I21" s="3">
-        <v>1515600</v>
+        <v>1007400</v>
       </c>
       <c r="J21" s="3">
+        <v>1571900</v>
+      </c>
+      <c r="K21" s="3">
         <v>974800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1259200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>374000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>517300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>473200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1085900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>220600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>271500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>345500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>125200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>267600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>260600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>163000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>372600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>468800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>527000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>673000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>497900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>399100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>491000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>435600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>46600</v>
+        <v>56300</v>
       </c>
       <c r="E22" s="3">
-        <v>43600</v>
+        <v>48300</v>
       </c>
       <c r="F22" s="3">
-        <v>43500</v>
+        <v>45200</v>
       </c>
       <c r="G22" s="3">
-        <v>27800</v>
+        <v>45200</v>
       </c>
       <c r="H22" s="3">
-        <v>24600</v>
+        <v>28800</v>
       </c>
       <c r="I22" s="3">
+        <v>25500</v>
+      </c>
+      <c r="J22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>20300</v>
+      </c>
+      <c r="L22" s="3">
+        <v>23100</v>
+      </c>
+      <c r="M22" s="3">
+        <v>23900</v>
+      </c>
+      <c r="N22" s="3">
+        <v>20600</v>
+      </c>
+      <c r="O22" s="3">
+        <v>23500</v>
+      </c>
+      <c r="P22" s="3">
+        <v>26200</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>26400</v>
+      </c>
+      <c r="R22" s="3">
+        <v>23400</v>
+      </c>
+      <c r="S22" s="3">
+        <v>22100</v>
+      </c>
+      <c r="T22" s="3">
         <v>27000</v>
       </c>
-      <c r="J22" s="3">
-        <v>20300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>23100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>23900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>20600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>23500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>26200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>26400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>23400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>22100</v>
-      </c>
-      <c r="S22" s="3">
-        <v>27000</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>25400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>25000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>30300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>13400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>5000</v>
+        <v>-238700</v>
       </c>
       <c r="E23" s="3">
-        <v>638900</v>
+        <v>5200</v>
       </c>
       <c r="F23" s="3">
-        <v>184800</v>
+        <v>662700</v>
       </c>
       <c r="G23" s="3">
-        <v>153300</v>
+        <v>191700</v>
       </c>
       <c r="H23" s="3">
-        <v>746900</v>
+        <v>159000</v>
       </c>
       <c r="I23" s="3">
-        <v>1290300</v>
+        <v>774600</v>
       </c>
       <c r="J23" s="3">
+        <v>1338300</v>
+      </c>
+      <c r="K23" s="3">
         <v>769700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1009300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>152400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>318800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>263600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>872200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-121600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-222900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-18500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-169300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-61300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>167200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>260400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>306600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>432500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>325100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>230100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>313900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>224900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>62200</v>
+        <v>24300</v>
       </c>
       <c r="E24" s="3">
-        <v>176500</v>
+        <v>64500</v>
       </c>
       <c r="F24" s="3">
-        <v>80200</v>
+        <v>183100</v>
       </c>
       <c r="G24" s="3">
-        <v>138900</v>
+        <v>83200</v>
       </c>
       <c r="H24" s="3">
-        <v>136200</v>
+        <v>144100</v>
       </c>
       <c r="I24" s="3">
-        <v>271700</v>
+        <v>141200</v>
       </c>
       <c r="J24" s="3">
+        <v>281800</v>
+      </c>
+      <c r="K24" s="3">
         <v>183400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>207400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>46500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>93300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>77000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>84700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>29100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-46300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>55000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>21200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>23500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>72600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>48400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>81300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>15600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>72300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>49100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>87200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-57200</v>
+        <v>-263000</v>
       </c>
       <c r="E26" s="3">
-        <v>462400</v>
+        <v>-59300</v>
       </c>
       <c r="F26" s="3">
-        <v>104600</v>
+        <v>479600</v>
       </c>
       <c r="G26" s="3">
-        <v>14400</v>
+        <v>108500</v>
       </c>
       <c r="H26" s="3">
-        <v>610700</v>
+        <v>14900</v>
       </c>
       <c r="I26" s="3">
-        <v>1018600</v>
+        <v>633400</v>
       </c>
       <c r="J26" s="3">
+        <v>1056500</v>
+      </c>
+      <c r="K26" s="3">
         <v>586400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>801900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>105900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>225500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>186600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>787500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-150600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-176600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-73500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-167400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-22100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-14000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-84700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>94500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>212000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>225300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>416800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>252900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>181000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>226700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>124400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-32700</v>
+        <v>-240600</v>
       </c>
       <c r="E27" s="3">
-        <v>476700</v>
+        <v>-34000</v>
       </c>
       <c r="F27" s="3">
-        <v>115700</v>
+        <v>494400</v>
       </c>
       <c r="G27" s="3">
-        <v>23000</v>
+        <v>120000</v>
       </c>
       <c r="H27" s="3">
-        <v>626600</v>
+        <v>23800</v>
       </c>
       <c r="I27" s="3">
-        <v>1031400</v>
+        <v>649900</v>
       </c>
       <c r="J27" s="3">
+        <v>1069700</v>
+      </c>
+      <c r="K27" s="3">
         <v>524900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>669900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>96700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>204900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>180700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>761500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-128000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-154900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-52700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-151500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-78200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>76800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>215600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>226900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>405100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>235900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>171800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>217300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>130700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2558,10 +2618,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2570,37 +2630,37 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>38300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-37700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-230600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-28600</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-81100</v>
+        <v>-31700</v>
       </c>
       <c r="E32" s="3">
-        <v>43500</v>
+        <v>-84100</v>
       </c>
       <c r="F32" s="3">
-        <v>158800</v>
+        <v>45200</v>
       </c>
       <c r="G32" s="3">
-        <v>-52600</v>
+        <v>164700</v>
       </c>
       <c r="H32" s="3">
-        <v>-70000</v>
+        <v>-54500</v>
       </c>
       <c r="I32" s="3">
-        <v>92800</v>
+        <v>-72600</v>
       </c>
       <c r="J32" s="3">
+        <v>96300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-221000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-83700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>62000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-54000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-65600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-184400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>152000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-62700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>426500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-52700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>170700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>51800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-20800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>51000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>27200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>30000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>38200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>77500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>102800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-32700</v>
+        <v>-240600</v>
       </c>
       <c r="E33" s="3">
-        <v>476700</v>
+        <v>-34000</v>
       </c>
       <c r="F33" s="3">
-        <v>115700</v>
+        <v>494400</v>
       </c>
       <c r="G33" s="3">
-        <v>26200</v>
+        <v>120000</v>
       </c>
       <c r="H33" s="3">
-        <v>626600</v>
+        <v>27200</v>
       </c>
       <c r="I33" s="3">
-        <v>1031400</v>
+        <v>649900</v>
       </c>
       <c r="J33" s="3">
+        <v>1069700</v>
+      </c>
+      <c r="K33" s="3">
         <v>524900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>670300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>94900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>243100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>143000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>531000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-126400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-183500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-52700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-151500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-78200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>76800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>215600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>226900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>405100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>235900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>171800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>217300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>130700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-32700</v>
+        <v>-240600</v>
       </c>
       <c r="E35" s="3">
-        <v>476700</v>
+        <v>-34000</v>
       </c>
       <c r="F35" s="3">
-        <v>115700</v>
+        <v>494400</v>
       </c>
       <c r="G35" s="3">
-        <v>26200</v>
+        <v>120000</v>
       </c>
       <c r="H35" s="3">
-        <v>626600</v>
+        <v>27200</v>
       </c>
       <c r="I35" s="3">
-        <v>1031400</v>
+        <v>649900</v>
       </c>
       <c r="J35" s="3">
+        <v>1069700</v>
+      </c>
+      <c r="K35" s="3">
         <v>524900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>670300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>94900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>243100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>143000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>531000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-126400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-183500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-52700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-151500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-78200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>76800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>215600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>226900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>405100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>235900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>171800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>217300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>130700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,192 +3437,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1747300</v>
+        <v>2335300</v>
       </c>
       <c r="E41" s="3">
-        <v>2053600</v>
+        <v>1812300</v>
       </c>
       <c r="F41" s="3">
-        <v>2823600</v>
+        <v>2129900</v>
       </c>
       <c r="G41" s="3">
-        <v>2726000</v>
+        <v>2928600</v>
       </c>
       <c r="H41" s="3">
-        <v>2364400</v>
+        <v>2827300</v>
       </c>
       <c r="I41" s="3">
-        <v>2241400</v>
+        <v>2452300</v>
       </c>
       <c r="J41" s="3">
+        <v>2324700</v>
+      </c>
+      <c r="K41" s="3">
         <v>1935400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1767600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1895000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1411900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1489200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1826900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1772200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1558500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1231800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1359800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1273500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1224500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>690500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>676400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>700300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>581300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>925500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>991000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>350000</v>
+        <v>430800</v>
       </c>
       <c r="E42" s="3">
-        <v>354900</v>
+        <v>363000</v>
       </c>
       <c r="F42" s="3">
-        <v>365700</v>
+        <v>368100</v>
       </c>
       <c r="G42" s="3">
-        <v>484700</v>
+        <v>379300</v>
       </c>
       <c r="H42" s="3">
-        <v>676600</v>
+        <v>502800</v>
       </c>
       <c r="I42" s="3">
-        <v>770600</v>
+        <v>701800</v>
       </c>
       <c r="J42" s="3">
+        <v>799200</v>
+      </c>
+      <c r="K42" s="3">
         <v>1217100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>740600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>401300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>439800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>463900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>472400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>602900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>587200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>279600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>177500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>196100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>180500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>183700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>200400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>195800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>216300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>200600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>244200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>259400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>600500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>580000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>624900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3578,150 +3670,156 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>2053100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1916200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2485800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2098400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2769100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2681000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2665200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2340300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2222700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2398100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2528700</v>
+        <v>2414100</v>
       </c>
       <c r="E44" s="3">
-        <v>2634800</v>
+        <v>2622700</v>
       </c>
       <c r="F44" s="3">
-        <v>2763600</v>
+        <v>2732700</v>
       </c>
       <c r="G44" s="3">
-        <v>2747000</v>
+        <v>2866300</v>
       </c>
       <c r="H44" s="3">
-        <v>2871300</v>
+        <v>2849100</v>
       </c>
       <c r="I44" s="3">
-        <v>2690300</v>
+        <v>2978000</v>
       </c>
       <c r="J44" s="3">
+        <v>2790300</v>
+      </c>
+      <c r="K44" s="3">
         <v>2308200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1783900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1547700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1346600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1420300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2019000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1953900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2064700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2275600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2303900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2609300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2626900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2830700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2987800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2446600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2285100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3731,11 +3829,11 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
@@ -3761,11 +3859,11 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>8</v>
@@ -3773,11 +3871,11 @@
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>8</v>
@@ -3794,8 +3892,8 @@
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
@@ -3803,385 +3901,400 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-      <c r="AD45" s="3" t="s">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3" t="s">
+      <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7039400</v>
+        <v>7589900</v>
       </c>
       <c r="E46" s="3">
-        <v>7563900</v>
+        <v>7301100</v>
       </c>
       <c r="F46" s="3">
-        <v>8545800</v>
+        <v>7845100</v>
       </c>
       <c r="G46" s="3">
-        <v>8151600</v>
+        <v>8863500</v>
       </c>
       <c r="H46" s="3">
-        <v>8513600</v>
+        <v>8454700</v>
       </c>
       <c r="I46" s="3">
-        <v>8369600</v>
+        <v>8830100</v>
       </c>
       <c r="J46" s="3">
+        <v>8680700</v>
+      </c>
+      <c r="K46" s="3">
         <v>7834500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6161000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5709900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4778100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5039700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6220500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6382300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6126600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6272800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5939600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6848100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6712900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6370100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6204900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5565400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5480700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2252900</v>
+        <v>2013700</v>
       </c>
       <c r="E47" s="3">
-        <v>2220400</v>
+        <v>2336700</v>
       </c>
       <c r="F47" s="3">
-        <v>2063900</v>
+        <v>2302900</v>
       </c>
       <c r="G47" s="3">
-        <v>1941000</v>
+        <v>2140600</v>
       </c>
       <c r="H47" s="3">
-        <v>2068200</v>
+        <v>2013100</v>
       </c>
       <c r="I47" s="3">
-        <v>1834200</v>
+        <v>2145100</v>
       </c>
       <c r="J47" s="3">
+        <v>1902400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1669800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1661200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1639100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1620400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1709100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1790700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1220500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1278300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1402500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1272900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1421300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1264500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1284800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1305300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1134900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1139600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6801600</v>
+        <v>7112700</v>
       </c>
       <c r="E48" s="3">
-        <v>6675200</v>
+        <v>7054500</v>
       </c>
       <c r="F48" s="3">
-        <v>6203500</v>
+        <v>6923400</v>
       </c>
       <c r="G48" s="3">
-        <v>5730500</v>
+        <v>6434100</v>
       </c>
       <c r="H48" s="3">
-        <v>5704300</v>
+        <v>5943500</v>
       </c>
       <c r="I48" s="3">
-        <v>5388800</v>
+        <v>5916300</v>
       </c>
       <c r="J48" s="3">
+        <v>5589200</v>
+      </c>
+      <c r="K48" s="3">
         <v>5176500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5139600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5300600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5068900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5346400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6654500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6955000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7139400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7892200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8217200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8909600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8463300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8251000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8390300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6777500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6821700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>989900</v>
+        <v>801300</v>
       </c>
       <c r="E49" s="3">
-        <v>934300</v>
+        <v>1026700</v>
       </c>
       <c r="F49" s="3">
-        <v>899900</v>
+        <v>969000</v>
       </c>
       <c r="G49" s="3">
-        <v>848700</v>
+        <v>933300</v>
       </c>
       <c r="H49" s="3">
-        <v>897200</v>
+        <v>880300</v>
       </c>
       <c r="I49" s="3">
-        <v>857300</v>
+        <v>930600</v>
       </c>
       <c r="J49" s="3">
+        <v>889200</v>
+      </c>
+      <c r="K49" s="3">
         <v>821900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>832600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>862900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>827400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>872700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>969200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1003200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1039500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1281300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1272900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1407600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1328000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1260400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1291000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1094100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1192800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>628400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>645800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>729800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>716500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1689300</v>
+        <v>2067400</v>
       </c>
       <c r="E52" s="3">
-        <v>1676200</v>
+        <v>1752100</v>
       </c>
       <c r="F52" s="3">
-        <v>1621100</v>
+        <v>1738500</v>
       </c>
       <c r="G52" s="3">
-        <v>1493700</v>
+        <v>1681400</v>
       </c>
       <c r="H52" s="3">
-        <v>1733300</v>
+        <v>1549300</v>
       </c>
       <c r="I52" s="3">
-        <v>1665900</v>
+        <v>1797700</v>
       </c>
       <c r="J52" s="3">
+        <v>1727800</v>
+      </c>
+      <c r="K52" s="3">
         <v>2033600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1719200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1577300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2964500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3126800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1394500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1241200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1246600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1307400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1493200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1516400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1538900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1473100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1415700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1311300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1237900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>18773100</v>
+        <v>19585000</v>
       </c>
       <c r="E54" s="3">
-        <v>19070000</v>
+        <v>19471000</v>
       </c>
       <c r="F54" s="3">
-        <v>19334200</v>
+        <v>19778900</v>
       </c>
       <c r="G54" s="3">
-        <v>18165600</v>
+        <v>20052900</v>
       </c>
       <c r="H54" s="3">
-        <v>18916600</v>
+        <v>18840900</v>
       </c>
       <c r="I54" s="3">
-        <v>18115800</v>
+        <v>19619800</v>
       </c>
       <c r="J54" s="3">
+        <v>18789300</v>
+      </c>
+      <c r="K54" s="3">
         <v>17536300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15513700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15089800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15259200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16094600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17029400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16802100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16830500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18156200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18195900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>20103100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19307700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18639300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18607200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15883200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15872800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2273700</v>
+        <v>2488400</v>
       </c>
       <c r="E57" s="3">
-        <v>2334900</v>
+        <v>2358200</v>
       </c>
       <c r="F57" s="3">
-        <v>2350700</v>
+        <v>2421700</v>
       </c>
       <c r="G57" s="3">
-        <v>2229200</v>
+        <v>2438100</v>
       </c>
       <c r="H57" s="3">
-        <v>2442300</v>
+        <v>2312100</v>
       </c>
       <c r="I57" s="3">
-        <v>2666600</v>
+        <v>2533000</v>
       </c>
       <c r="J57" s="3">
+        <v>2765700</v>
+      </c>
+      <c r="K57" s="3">
         <v>2298400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1901800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1909600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1642500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1732400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1962600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1809700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1691000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2183800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2068800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2373000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2429800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2507100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2299400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2036400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2184200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>527200</v>
+        <v>674500</v>
       </c>
       <c r="E58" s="3">
-        <v>482100</v>
+        <v>546800</v>
       </c>
       <c r="F58" s="3">
-        <v>539500</v>
+        <v>500000</v>
       </c>
       <c r="G58" s="3">
-        <v>617000</v>
+        <v>559600</v>
       </c>
       <c r="H58" s="3">
-        <v>1013800</v>
+        <v>639900</v>
       </c>
       <c r="I58" s="3">
-        <v>713000</v>
+        <v>1051500</v>
       </c>
       <c r="J58" s="3">
+        <v>739500</v>
+      </c>
+      <c r="K58" s="3">
         <v>646800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>393700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>393500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>442200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>466400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>491800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>700500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>718600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>782800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>681500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>731100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>945500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1009000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1057500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>675900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>508300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>571600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>954700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>433200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>429200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>404800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1014700</v>
+        <v>1000700</v>
       </c>
       <c r="E59" s="3">
-        <v>877400</v>
+        <v>1052400</v>
       </c>
       <c r="F59" s="3">
-        <v>982400</v>
+        <v>910000</v>
       </c>
       <c r="G59" s="3">
-        <v>1068900</v>
+        <v>1018900</v>
       </c>
       <c r="H59" s="3">
-        <v>1065800</v>
+        <v>1108600</v>
       </c>
       <c r="I59" s="3">
-        <v>980800</v>
+        <v>1105400</v>
       </c>
       <c r="J59" s="3">
+        <v>1017300</v>
+      </c>
+      <c r="K59" s="3">
         <v>1146500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>663900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>488300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>379600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>554400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>370700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>376900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>483300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>535900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>492900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>426400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>529000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>684000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>603300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>509000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>526400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>410100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>337100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>411300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>458100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3815500</v>
+        <v>4163600</v>
       </c>
       <c r="E60" s="3">
-        <v>3694300</v>
+        <v>3957400</v>
       </c>
       <c r="F60" s="3">
-        <v>3872600</v>
+        <v>3831700</v>
       </c>
       <c r="G60" s="3">
-        <v>3915100</v>
+        <v>4016600</v>
       </c>
       <c r="H60" s="3">
-        <v>4521900</v>
+        <v>4060700</v>
       </c>
       <c r="I60" s="3">
-        <v>4360400</v>
+        <v>4690000</v>
       </c>
       <c r="J60" s="3">
+        <v>4522500</v>
+      </c>
+      <c r="K60" s="3">
         <v>4091700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2959400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2791300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2464300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2599200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3008800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2880900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2786600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3450000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3286200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3597000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3801800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4045200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4040900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3315500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3201600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2738700</v>
+        <v>2748900</v>
       </c>
       <c r="E61" s="3">
-        <v>2721500</v>
+        <v>2840500</v>
       </c>
       <c r="F61" s="3">
-        <v>2708600</v>
+        <v>2822700</v>
       </c>
       <c r="G61" s="3">
-        <v>2380600</v>
+        <v>2809300</v>
       </c>
       <c r="H61" s="3">
-        <v>1901500</v>
+        <v>2469100</v>
       </c>
       <c r="I61" s="3">
-        <v>1925600</v>
+        <v>1972100</v>
       </c>
       <c r="J61" s="3">
+        <v>1997200</v>
+      </c>
+      <c r="K61" s="3">
         <v>1927300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2398100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2310300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2225300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2347100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2569900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2620900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2694100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2156700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2087200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2405400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2153000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1195400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1054000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>806700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>959300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>948900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>356300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>368600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>415900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>550400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2364100</v>
+        <v>2505300</v>
       </c>
       <c r="E62" s="3">
-        <v>2425200</v>
+        <v>2452000</v>
       </c>
       <c r="F62" s="3">
-        <v>2293700</v>
+        <v>2515300</v>
       </c>
       <c r="G62" s="3">
-        <v>2010700</v>
+        <v>2379000</v>
       </c>
       <c r="H62" s="3">
-        <v>2149500</v>
+        <v>2085400</v>
       </c>
       <c r="I62" s="3">
-        <v>2223300</v>
+        <v>2229400</v>
       </c>
       <c r="J62" s="3">
+        <v>2306000</v>
+      </c>
+      <c r="K62" s="3">
         <v>2416100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2541500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2318000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3260900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3439400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3429000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3510900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3361000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3719000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3516400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3912800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3455400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3278400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3547300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2811300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2795200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>9346900</v>
+        <v>10044200</v>
       </c>
       <c r="E66" s="3">
-        <v>9295400</v>
+        <v>9694400</v>
       </c>
       <c r="F66" s="3">
-        <v>9403300</v>
+        <v>9640900</v>
       </c>
       <c r="G66" s="3">
-        <v>8795100</v>
+        <v>9752800</v>
       </c>
       <c r="H66" s="3">
-        <v>9118600</v>
+        <v>9122000</v>
       </c>
       <c r="I66" s="3">
-        <v>9029600</v>
+        <v>9457500</v>
       </c>
       <c r="J66" s="3">
+        <v>9365200</v>
+      </c>
+      <c r="K66" s="3">
         <v>8947600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8220700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7761700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8228700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8679200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9335600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9322800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9168900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9726700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9348900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10441200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9925000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9051500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8925000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7391100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7415000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5750500</v>
+        <v>5774800</v>
       </c>
       <c r="E72" s="3">
-        <v>5798400</v>
+        <v>5964300</v>
       </c>
       <c r="F72" s="3">
-        <v>6534300</v>
+        <v>6013900</v>
       </c>
       <c r="G72" s="3">
-        <v>6435100</v>
+        <v>6777200</v>
       </c>
       <c r="H72" s="3">
-        <v>6394800</v>
+        <v>6674300</v>
       </c>
       <c r="I72" s="3">
-        <v>6040500</v>
+        <v>6632500</v>
       </c>
       <c r="J72" s="3">
+        <v>6265000</v>
+      </c>
+      <c r="K72" s="3">
         <v>6022700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4972300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4877400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5029300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5304700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5389100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5010800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5033300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5159600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5837800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6405600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6299500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6466900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6443600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5915000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5838300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9426100</v>
+        <v>9540800</v>
       </c>
       <c r="E76" s="3">
-        <v>9774600</v>
+        <v>9776600</v>
       </c>
       <c r="F76" s="3">
-        <v>9930900</v>
+        <v>10138000</v>
       </c>
       <c r="G76" s="3">
-        <v>9370500</v>
+        <v>10300100</v>
       </c>
       <c r="H76" s="3">
-        <v>9798000</v>
+        <v>9718900</v>
       </c>
       <c r="I76" s="3">
-        <v>9086300</v>
+        <v>10162300</v>
       </c>
       <c r="J76" s="3">
+        <v>9424100</v>
+      </c>
+      <c r="K76" s="3">
         <v>8588600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7292900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7328000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7030500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7415500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7693800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7479300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7661600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8429500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8847000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9661900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9382700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9587900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9682200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8492100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8457800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-32700</v>
+        <v>-240600</v>
       </c>
       <c r="E81" s="3">
-        <v>476700</v>
+        <v>-34000</v>
       </c>
       <c r="F81" s="3">
-        <v>115700</v>
+        <v>494400</v>
       </c>
       <c r="G81" s="3">
-        <v>26200</v>
+        <v>120000</v>
       </c>
       <c r="H81" s="3">
-        <v>626600</v>
+        <v>27200</v>
       </c>
       <c r="I81" s="3">
-        <v>1031400</v>
+        <v>649900</v>
       </c>
       <c r="J81" s="3">
+        <v>1069700</v>
+      </c>
+      <c r="K81" s="3">
         <v>524900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>670300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>94900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>243100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>143000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>531000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-126400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-183500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-52700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-151500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-78200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>76800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>215600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>226900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>405100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>235900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>171800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>217300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>130700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>212800</v>
+        <v>660400</v>
       </c>
       <c r="E83" s="3">
-        <v>214000</v>
+        <v>220700</v>
       </c>
       <c r="F83" s="3">
-        <v>199900</v>
+        <v>222000</v>
       </c>
       <c r="G83" s="3">
-        <v>233800</v>
+        <v>207400</v>
       </c>
       <c r="H83" s="3">
-        <v>199800</v>
+        <v>242500</v>
       </c>
       <c r="I83" s="3">
-        <v>198300</v>
+        <v>207300</v>
       </c>
       <c r="J83" s="3">
+        <v>205700</v>
+      </c>
+      <c r="K83" s="3">
         <v>184700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>226800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>197700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>178000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>186100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>415700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>211200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>222800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>337000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>269100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>243500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>237500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>193900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>189400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>193300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>207100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>228100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>168000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>160800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>166700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>197300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>465300</v>
+        <v>296900</v>
       </c>
       <c r="E89" s="3">
-        <v>924700</v>
+        <v>482600</v>
       </c>
       <c r="F89" s="3">
-        <v>338800</v>
+        <v>959000</v>
       </c>
       <c r="G89" s="3">
-        <v>769100</v>
+        <v>351400</v>
       </c>
       <c r="H89" s="3">
-        <v>550300</v>
+        <v>797700</v>
       </c>
       <c r="I89" s="3">
-        <v>1380900</v>
+        <v>570800</v>
       </c>
       <c r="J89" s="3">
+        <v>1432200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-17100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>791900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>615000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-54000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>563900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>457800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>221800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>138000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>628700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>420200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>300600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>88200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>106500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>263300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>155300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>215800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>740900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>341600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>501400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>82400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>523700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4329000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3200000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3476000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2633000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-182900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-116400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-136900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-320200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-237200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-258000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-184600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-284000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-183700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-157200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-689000</v>
+        <v>-508400</v>
       </c>
       <c r="E94" s="3">
-        <v>-434700</v>
+        <v>-714600</v>
       </c>
       <c r="F94" s="3">
-        <v>-284700</v>
+        <v>-450900</v>
       </c>
       <c r="G94" s="3">
-        <v>-387200</v>
+        <v>-295300</v>
       </c>
       <c r="H94" s="3">
-        <v>-380500</v>
+        <v>-401600</v>
       </c>
       <c r="I94" s="3">
-        <v>-44100</v>
+        <v>-394600</v>
       </c>
       <c r="J94" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-154100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-265300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-138800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>85700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-128800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>12700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-131700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-456900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-194500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-324000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-234000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-310700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-182800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-292200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-154800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-165900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>220100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7894,41 +8127,41 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-1150000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-1192800</v>
       </c>
       <c r="G96" s="3">
-        <v>-10900</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-282300</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-1051400</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>-241200</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-272200</v>
       </c>
-      <c r="I96" s="3">
-        <v>-1013700</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-24300</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-241200</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-272200</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -7936,49 +8169,52 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-10100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-295800</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-2500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-366300</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-41300</v>
+        <v>806700</v>
       </c>
       <c r="E100" s="3">
-        <v>-1314000</v>
+        <v>-42900</v>
       </c>
       <c r="F100" s="3">
-        <v>-35200</v>
+        <v>-1362900</v>
       </c>
       <c r="G100" s="3">
-        <v>21300</v>
+        <v>-36500</v>
       </c>
       <c r="H100" s="3">
-        <v>-114100</v>
+        <v>22100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1104900</v>
+        <v>-118400</v>
       </c>
       <c r="J100" s="3">
+        <v>-1146000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-13800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-151900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>38200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-250200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-49300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-493200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-73900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>669000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-107400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-208300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>531200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>115200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>45700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>22200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-344300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>101800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>602000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>26000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-41200</v>
+        <v>-72200</v>
       </c>
       <c r="E101" s="3">
-        <v>54000</v>
+        <v>-42800</v>
       </c>
       <c r="F101" s="3">
-        <v>78800</v>
+        <v>56000</v>
       </c>
       <c r="G101" s="3">
-        <v>-41600</v>
+        <v>81800</v>
       </c>
       <c r="H101" s="3">
-        <v>67300</v>
+        <v>-43200</v>
       </c>
       <c r="I101" s="3">
-        <v>74200</v>
+        <v>69800</v>
       </c>
       <c r="J101" s="3">
+        <v>76900</v>
+      </c>
+      <c r="K101" s="3">
         <v>23900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>13900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-19000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>32500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-28500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-33400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-95400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>58500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-8600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>21100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>44000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-22400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>31000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>9000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>30300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-306200</v>
+        <v>523000</v>
       </c>
       <c r="E102" s="3">
-        <v>-770100</v>
+        <v>-317600</v>
       </c>
       <c r="F102" s="3">
-        <v>97700</v>
+        <v>-798700</v>
       </c>
       <c r="G102" s="3">
-        <v>361500</v>
+        <v>101300</v>
       </c>
       <c r="H102" s="3">
-        <v>123000</v>
+        <v>375000</v>
       </c>
       <c r="I102" s="3">
-        <v>306000</v>
+        <v>127600</v>
       </c>
       <c r="J102" s="3">
+        <v>317400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-161200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>388600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-127500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>483000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-260500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>213700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>326700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>188700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>519300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>11800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-96000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>119100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-377400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>36500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>10500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-156300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4435100</v>
+        <v>4497300</v>
       </c>
       <c r="E8" s="3">
-        <v>4240400</v>
+        <v>4422500</v>
       </c>
       <c r="F8" s="3">
-        <v>5087300</v>
+        <v>4228400</v>
       </c>
       <c r="G8" s="3">
-        <v>4603900</v>
+        <v>5072900</v>
       </c>
       <c r="H8" s="3">
-        <v>4181000</v>
+        <v>4590800</v>
       </c>
       <c r="I8" s="3">
-        <v>4974900</v>
+        <v>4169100</v>
       </c>
       <c r="J8" s="3">
+        <v>4960800</v>
+      </c>
+      <c r="K8" s="3">
         <v>6146300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4263500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4367500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3452900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3250600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3169900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1249900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2787400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2567200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3202000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3928000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4515500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4529900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4254800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4330700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4068100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2811000</v>
+        <v>2840100</v>
       </c>
       <c r="E9" s="3">
-        <v>2893300</v>
+        <v>2803000</v>
       </c>
       <c r="F9" s="3">
-        <v>3045900</v>
+        <v>2885100</v>
       </c>
       <c r="G9" s="3">
-        <v>2968600</v>
+        <v>3037200</v>
       </c>
       <c r="H9" s="3">
-        <v>2737400</v>
+        <v>2960200</v>
       </c>
       <c r="I9" s="3">
-        <v>3256100</v>
+        <v>2729600</v>
       </c>
       <c r="J9" s="3">
+        <v>3246800</v>
+      </c>
+      <c r="K9" s="3">
         <v>3512800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2667000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2333100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2229300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1995300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1897500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>625800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1676100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1603700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1894400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2471300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2899500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2997100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2845600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2839000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2625700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1624100</v>
+        <v>1657200</v>
       </c>
       <c r="E10" s="3">
-        <v>1347100</v>
+        <v>1619500</v>
       </c>
       <c r="F10" s="3">
-        <v>2041500</v>
+        <v>1343300</v>
       </c>
       <c r="G10" s="3">
-        <v>1635300</v>
+        <v>2035700</v>
       </c>
       <c r="H10" s="3">
-        <v>1443600</v>
+        <v>1630600</v>
       </c>
       <c r="I10" s="3">
-        <v>1718900</v>
+        <v>1439500</v>
       </c>
       <c r="J10" s="3">
+        <v>1714000</v>
+      </c>
+      <c r="K10" s="3">
         <v>2633500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1596500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2034400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1223600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1255300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1272400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>624100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1111300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>963600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1307600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1456800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1616100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1532800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1409100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1491700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1442300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>929900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>969000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,64 +1318,67 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>419700</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>418500</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-300</v>
       </c>
-      <c r="H14" s="3">
-        <v>27200</v>
-      </c>
       <c r="I14" s="3">
+        <v>27100</v>
+      </c>
+      <c r="J14" s="3">
         <v>4600</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>27700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>185300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100900</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1375,11 +1395,11 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1396,103 +1416,109 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>240800</v>
+        <v>233800</v>
       </c>
       <c r="E15" s="3">
-        <v>220700</v>
+        <v>240100</v>
       </c>
       <c r="F15" s="3">
-        <v>222000</v>
+        <v>220100</v>
       </c>
       <c r="G15" s="3">
-        <v>207600</v>
+        <v>221300</v>
       </c>
       <c r="H15" s="3">
-        <v>215300</v>
+        <v>207100</v>
       </c>
       <c r="I15" s="3">
-        <v>202600</v>
+        <v>214700</v>
       </c>
       <c r="J15" s="3">
+        <v>202000</v>
+      </c>
+      <c r="K15" s="3">
         <v>205600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>184700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>199100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>196400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>177300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>174000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>88100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>173300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>184400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>192100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>236000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>269100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>243400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>237500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>193900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>189400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>193400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>207100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>228100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>167900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>160800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>166700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>197200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4649200</v>
+        <v>4207300</v>
       </c>
       <c r="E17" s="3">
-        <v>4271100</v>
+        <v>4636000</v>
       </c>
       <c r="F17" s="3">
-        <v>4334200</v>
+        <v>4258900</v>
       </c>
       <c r="G17" s="3">
-        <v>4202400</v>
+        <v>4321900</v>
       </c>
       <c r="H17" s="3">
-        <v>4047700</v>
+        <v>4190400</v>
       </c>
       <c r="I17" s="3">
-        <v>4247400</v>
+        <v>4036200</v>
       </c>
       <c r="J17" s="3">
+        <v>4235300</v>
+      </c>
+      <c r="K17" s="3">
         <v>4683700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3694400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3418800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3214700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2965200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2948300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>535800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2595600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2728100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2976300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3972200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4488800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4454100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4252500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4310600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3857600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-214100</v>
+        <v>290000</v>
       </c>
       <c r="E18" s="3">
+        <v>-213500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-30600</v>
       </c>
-      <c r="F18" s="3">
-        <v>753100</v>
-      </c>
       <c r="G18" s="3">
-        <v>401500</v>
+        <v>751000</v>
       </c>
       <c r="H18" s="3">
-        <v>133300</v>
+        <v>400400</v>
       </c>
       <c r="I18" s="3">
-        <v>727600</v>
+        <v>132900</v>
       </c>
       <c r="J18" s="3">
+        <v>725500</v>
+      </c>
+      <c r="K18" s="3">
         <v>1462600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>569100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>948700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>238300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>285400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>221500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>714100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>191800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-160900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>225700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-44200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>26700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>75900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>210400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>305500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>358100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>522300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>269000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>341100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>297200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>242200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>31700</v>
+        <v>-125000</v>
       </c>
       <c r="E20" s="3">
-        <v>84100</v>
+        <v>31600</v>
       </c>
       <c r="F20" s="3">
-        <v>-45200</v>
+        <v>83900</v>
       </c>
       <c r="G20" s="3">
-        <v>-164700</v>
+        <v>-45000</v>
       </c>
       <c r="H20" s="3">
-        <v>54500</v>
+        <v>-164200</v>
       </c>
       <c r="I20" s="3">
-        <v>72600</v>
+        <v>54400</v>
       </c>
       <c r="J20" s="3">
+        <v>72400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-96300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>221000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>83700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-62000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>54000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>65600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>184400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-152000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>62700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-426500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>52700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-170700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-51800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>20800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-51000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>60900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>27100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>478000</v>
+        <v>398900</v>
       </c>
       <c r="E21" s="3">
-        <v>274200</v>
+        <v>476600</v>
       </c>
       <c r="F21" s="3">
-        <v>929900</v>
+        <v>273500</v>
       </c>
       <c r="G21" s="3">
-        <v>444200</v>
+        <v>927300</v>
       </c>
       <c r="H21" s="3">
-        <v>430300</v>
+        <v>443000</v>
       </c>
       <c r="I21" s="3">
-        <v>1007400</v>
+        <v>429100</v>
       </c>
       <c r="J21" s="3">
+        <v>1004500</v>
+      </c>
+      <c r="K21" s="3">
         <v>1571900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>974800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1259200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>374000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>517300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>473200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1085900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>220600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>271500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>345500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>125200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>267600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>260600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>163000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>372600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>468800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>527000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>673000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>497900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>399100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>491000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>435600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>56300</v>
+        <v>56500</v>
       </c>
       <c r="E22" s="3">
-        <v>48300</v>
+        <v>56100</v>
       </c>
       <c r="F22" s="3">
-        <v>45200</v>
+        <v>48100</v>
       </c>
       <c r="G22" s="3">
-        <v>45200</v>
+        <v>45100</v>
       </c>
       <c r="H22" s="3">
+        <v>45000</v>
+      </c>
+      <c r="I22" s="3">
         <v>28800</v>
       </c>
-      <c r="I22" s="3">
-        <v>25500</v>
-      </c>
       <c r="J22" s="3">
+        <v>25400</v>
+      </c>
+      <c r="K22" s="3">
         <v>28000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>26400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>22100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>27000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>25400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>25000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>30300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>13400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-238700</v>
+        <v>108600</v>
       </c>
       <c r="E23" s="3">
+        <v>-238000</v>
+      </c>
+      <c r="F23" s="3">
         <v>5200</v>
       </c>
-      <c r="F23" s="3">
-        <v>662700</v>
-      </c>
       <c r="G23" s="3">
-        <v>191700</v>
+        <v>660800</v>
       </c>
       <c r="H23" s="3">
-        <v>159000</v>
+        <v>191200</v>
       </c>
       <c r="I23" s="3">
-        <v>774600</v>
+        <v>158500</v>
       </c>
       <c r="J23" s="3">
+        <v>772400</v>
+      </c>
+      <c r="K23" s="3">
         <v>1338300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>769700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1009300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>152400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>318800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>263600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>872200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-121600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-222900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-169300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-61300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>167200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>260400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>306600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>432500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>325100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>230100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>313900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>224900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>24300</v>
+        <v>68100</v>
       </c>
       <c r="E24" s="3">
-        <v>64500</v>
+        <v>24200</v>
       </c>
       <c r="F24" s="3">
-        <v>183100</v>
+        <v>64300</v>
       </c>
       <c r="G24" s="3">
-        <v>83200</v>
+        <v>182600</v>
       </c>
       <c r="H24" s="3">
-        <v>144100</v>
+        <v>83000</v>
       </c>
       <c r="I24" s="3">
-        <v>141200</v>
+        <v>143700</v>
       </c>
       <c r="J24" s="3">
+        <v>140800</v>
+      </c>
+      <c r="K24" s="3">
         <v>281800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>183400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>207400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>93300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>77000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>84700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>29100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-46300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>55000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>21200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>17000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>23500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>72600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>48400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>81300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>15600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>72300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>49100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>87200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>100500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-263000</v>
+        <v>40500</v>
       </c>
       <c r="E26" s="3">
-        <v>-59300</v>
+        <v>-262200</v>
       </c>
       <c r="F26" s="3">
-        <v>479600</v>
+        <v>-59100</v>
       </c>
       <c r="G26" s="3">
-        <v>108500</v>
+        <v>478200</v>
       </c>
       <c r="H26" s="3">
+        <v>108200</v>
+      </c>
+      <c r="I26" s="3">
         <v>14900</v>
       </c>
-      <c r="I26" s="3">
-        <v>633400</v>
-      </c>
       <c r="J26" s="3">
+        <v>631600</v>
+      </c>
+      <c r="K26" s="3">
         <v>1056500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>586400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>801900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>105900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>225500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>186600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>787500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-11100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-150600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-176600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-73500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-167400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-22100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-84700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>94500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>212000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>225300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>416800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>252900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>181000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>226700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>124400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-240600</v>
+        <v>89000</v>
       </c>
       <c r="E27" s="3">
-        <v>-34000</v>
+        <v>-239900</v>
       </c>
       <c r="F27" s="3">
-        <v>494400</v>
+        <v>-33900</v>
       </c>
       <c r="G27" s="3">
-        <v>120000</v>
+        <v>493000</v>
       </c>
       <c r="H27" s="3">
-        <v>23800</v>
+        <v>119700</v>
       </c>
       <c r="I27" s="3">
-        <v>649900</v>
+        <v>23700</v>
       </c>
       <c r="J27" s="3">
+        <v>648000</v>
+      </c>
+      <c r="K27" s="3">
         <v>1069700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>524900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>669900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>96700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>204900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>180700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>761500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-11300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-128000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-154900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-52700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-151500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-78200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>76800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>215600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>226900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>405100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>235900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>171800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>217300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>130700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,13 +2661,16 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2621,11 +2682,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>3400</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
@@ -2633,37 +2694,37 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>38300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-37700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-230600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-11200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>1600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-28600</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-31700</v>
+        <v>125000</v>
       </c>
       <c r="E32" s="3">
-        <v>-84100</v>
+        <v>-31600</v>
       </c>
       <c r="F32" s="3">
-        <v>45200</v>
+        <v>-83900</v>
       </c>
       <c r="G32" s="3">
-        <v>164700</v>
+        <v>45000</v>
       </c>
       <c r="H32" s="3">
-        <v>-54500</v>
+        <v>164200</v>
       </c>
       <c r="I32" s="3">
-        <v>-72600</v>
+        <v>-54400</v>
       </c>
       <c r="J32" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="K32" s="3">
         <v>96300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-221000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-83700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>62000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-54000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-65600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-184400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>152000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-62700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>426500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-52700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>170700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>51800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-20800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>51000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>27200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>30000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>38200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>77500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>102800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-240600</v>
+        <v>89000</v>
       </c>
       <c r="E33" s="3">
-        <v>-34000</v>
+        <v>-239900</v>
       </c>
       <c r="F33" s="3">
-        <v>494400</v>
+        <v>-33900</v>
       </c>
       <c r="G33" s="3">
-        <v>120000</v>
+        <v>493000</v>
       </c>
       <c r="H33" s="3">
-        <v>27200</v>
+        <v>119700</v>
       </c>
       <c r="I33" s="3">
-        <v>649900</v>
+        <v>27100</v>
       </c>
       <c r="J33" s="3">
+        <v>648000</v>
+      </c>
+      <c r="K33" s="3">
         <v>1069700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>524900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>670300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>94900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>243100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>143000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>531000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-22600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-126400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-183500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-52700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-151500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-78200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>76800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>215600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>226900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>405100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>235900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>171800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>217300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>130700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-240600</v>
+        <v>89000</v>
       </c>
       <c r="E35" s="3">
-        <v>-34000</v>
+        <v>-239900</v>
       </c>
       <c r="F35" s="3">
-        <v>494400</v>
+        <v>-33900</v>
       </c>
       <c r="G35" s="3">
-        <v>120000</v>
+        <v>493000</v>
       </c>
       <c r="H35" s="3">
-        <v>27200</v>
+        <v>119700</v>
       </c>
       <c r="I35" s="3">
-        <v>649900</v>
+        <v>27100</v>
       </c>
       <c r="J35" s="3">
+        <v>648000</v>
+      </c>
+      <c r="K35" s="3">
         <v>1069700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>524900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>670300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>94900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>243100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>143000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>531000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-22600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-126400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-183500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-52700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-151500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-78200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>76800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>215600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>226900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>405100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>235900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>171800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>217300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>130700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,198 +3524,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2335300</v>
+        <v>1856000</v>
       </c>
       <c r="E41" s="3">
-        <v>1812300</v>
+        <v>2328600</v>
       </c>
       <c r="F41" s="3">
-        <v>2129900</v>
+        <v>1807100</v>
       </c>
       <c r="G41" s="3">
-        <v>2928600</v>
+        <v>2123800</v>
       </c>
       <c r="H41" s="3">
-        <v>2827300</v>
+        <v>2920300</v>
       </c>
       <c r="I41" s="3">
-        <v>2452300</v>
+        <v>2819300</v>
       </c>
       <c r="J41" s="3">
+        <v>2445300</v>
+      </c>
+      <c r="K41" s="3">
         <v>2324700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1935400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1767600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1895000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1411900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1489200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1826900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1772200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1558500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1231800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1359800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1273500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1224500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>690500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>676400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>700300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>581300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>925500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>991000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>430800</v>
+        <v>597600</v>
       </c>
       <c r="E42" s="3">
-        <v>363000</v>
+        <v>429500</v>
       </c>
       <c r="F42" s="3">
-        <v>368100</v>
+        <v>362000</v>
       </c>
       <c r="G42" s="3">
-        <v>379300</v>
+        <v>367000</v>
       </c>
       <c r="H42" s="3">
-        <v>502800</v>
+        <v>378200</v>
       </c>
       <c r="I42" s="3">
-        <v>701800</v>
+        <v>501300</v>
       </c>
       <c r="J42" s="3">
+        <v>699800</v>
+      </c>
+      <c r="K42" s="3">
         <v>799200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1217100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>740600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>401300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>439800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>463900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>472400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>602900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>587200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>279600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>177500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>196100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>180500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>183700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>200400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>195800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>216300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>200600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>244200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>259400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>600500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>580000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>624900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3673,153 +3766,159 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>2053100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1916200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2485800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2098400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2769100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2681000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2665200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2340300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2222700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2414100</v>
+        <v>2392300</v>
       </c>
       <c r="E44" s="3">
-        <v>2622700</v>
+        <v>2407200</v>
       </c>
       <c r="F44" s="3">
-        <v>2732700</v>
+        <v>2615200</v>
       </c>
       <c r="G44" s="3">
-        <v>2866300</v>
+        <v>2724900</v>
       </c>
       <c r="H44" s="3">
-        <v>2849100</v>
+        <v>2858100</v>
       </c>
       <c r="I44" s="3">
-        <v>2978000</v>
+        <v>2841000</v>
       </c>
       <c r="J44" s="3">
+        <v>2969600</v>
+      </c>
+      <c r="K44" s="3">
         <v>2790300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2308200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1783900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1547700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1346600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1420300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2019000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1953900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2064700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2275600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2303900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2609300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2626900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2830700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2987800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2446600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3832,11 +3931,11 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>100</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -3862,11 +3961,11 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>100</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>8</v>
@@ -3874,11 +3973,11 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V45" s="3">
         <v>100</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
@@ -3895,8 +3994,8 @@
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -3904,397 +4003,412 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-      <c r="AE45" s="3" t="s">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3" t="s">
+      <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7589900</v>
+        <v>7586100</v>
       </c>
       <c r="E46" s="3">
-        <v>7301100</v>
+        <v>7568300</v>
       </c>
       <c r="F46" s="3">
-        <v>7845100</v>
+        <v>7280300</v>
       </c>
       <c r="G46" s="3">
-        <v>8863500</v>
+        <v>7822800</v>
       </c>
       <c r="H46" s="3">
-        <v>8454700</v>
+        <v>8838300</v>
       </c>
       <c r="I46" s="3">
-        <v>8830100</v>
+        <v>8430600</v>
       </c>
       <c r="J46" s="3">
+        <v>8805000</v>
+      </c>
+      <c r="K46" s="3">
         <v>8680700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7834500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6161000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5709900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4778100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5039700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6220500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6382300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6126600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6272800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5939600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6848100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6712900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6370100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6204900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5565400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2013700</v>
+        <v>2129400</v>
       </c>
       <c r="E47" s="3">
-        <v>2336700</v>
+        <v>2008000</v>
       </c>
       <c r="F47" s="3">
-        <v>2302900</v>
+        <v>2330000</v>
       </c>
       <c r="G47" s="3">
-        <v>2140600</v>
+        <v>2296400</v>
       </c>
       <c r="H47" s="3">
-        <v>2013100</v>
+        <v>2134500</v>
       </c>
       <c r="I47" s="3">
-        <v>2145100</v>
+        <v>2007400</v>
       </c>
       <c r="J47" s="3">
+        <v>2139000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1902400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1669800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1661200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1639100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1620400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1709100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1790700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1220500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1278300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1402500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1272900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1421300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1264500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1284800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1305300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1134900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7112700</v>
+        <v>7315000</v>
       </c>
       <c r="E48" s="3">
-        <v>7054500</v>
+        <v>7092500</v>
       </c>
       <c r="F48" s="3">
-        <v>6923400</v>
+        <v>7034400</v>
       </c>
       <c r="G48" s="3">
-        <v>6434100</v>
+        <v>6903700</v>
       </c>
       <c r="H48" s="3">
-        <v>5943500</v>
+        <v>6415800</v>
       </c>
       <c r="I48" s="3">
-        <v>5916300</v>
+        <v>5926600</v>
       </c>
       <c r="J48" s="3">
+        <v>5899500</v>
+      </c>
+      <c r="K48" s="3">
         <v>5589200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5176500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5139600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5300600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5068900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5346400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6654500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6955000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7139400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7892200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8217200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8909600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8463300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8251000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8390300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6777500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>801300</v>
+        <v>826800</v>
       </c>
       <c r="E49" s="3">
-        <v>1026700</v>
+        <v>799000</v>
       </c>
       <c r="F49" s="3">
-        <v>969000</v>
+        <v>1023700</v>
       </c>
       <c r="G49" s="3">
-        <v>933300</v>
+        <v>966200</v>
       </c>
       <c r="H49" s="3">
-        <v>880300</v>
+        <v>930700</v>
       </c>
       <c r="I49" s="3">
-        <v>930600</v>
+        <v>877800</v>
       </c>
       <c r="J49" s="3">
+        <v>927900</v>
+      </c>
+      <c r="K49" s="3">
         <v>889200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>821900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>832600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>862900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>827400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>872700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>969200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1003200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1039500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1281300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1272900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1407600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1328000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1260400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1291000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1094100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>628400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>645800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>729800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>716500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2067400</v>
+        <v>2302900</v>
       </c>
       <c r="E52" s="3">
-        <v>1752100</v>
+        <v>2061500</v>
       </c>
       <c r="F52" s="3">
-        <v>1738500</v>
+        <v>1747100</v>
       </c>
       <c r="G52" s="3">
-        <v>1681400</v>
+        <v>1733600</v>
       </c>
       <c r="H52" s="3">
-        <v>1549300</v>
+        <v>1676600</v>
       </c>
       <c r="I52" s="3">
-        <v>1797700</v>
+        <v>1544800</v>
       </c>
       <c r="J52" s="3">
+        <v>1792600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1727800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2033600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1719200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1577300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2964500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3126800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1394500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1241200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1246600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1307400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1493200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1516400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1538900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1473100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1415700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1311300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19585000</v>
+        <v>20160300</v>
       </c>
       <c r="E54" s="3">
-        <v>19471000</v>
+        <v>19529200</v>
       </c>
       <c r="F54" s="3">
-        <v>19778900</v>
+        <v>19415500</v>
       </c>
       <c r="G54" s="3">
-        <v>20052900</v>
+        <v>19722600</v>
       </c>
       <c r="H54" s="3">
-        <v>18840900</v>
+        <v>19995900</v>
       </c>
       <c r="I54" s="3">
-        <v>19619800</v>
+        <v>18787300</v>
       </c>
       <c r="J54" s="3">
+        <v>19564000</v>
+      </c>
+      <c r="K54" s="3">
         <v>18789300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17536300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15513700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15089800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15259200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16094600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17029400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16802100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16830500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18156200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18195900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>20103100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19307700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18639300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18607200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15883200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2488400</v>
+        <v>2510500</v>
       </c>
       <c r="E57" s="3">
-        <v>2358200</v>
+        <v>2481300</v>
       </c>
       <c r="F57" s="3">
-        <v>2421700</v>
+        <v>2351500</v>
       </c>
       <c r="G57" s="3">
-        <v>2438100</v>
+        <v>2414800</v>
       </c>
       <c r="H57" s="3">
-        <v>2312100</v>
+        <v>2431200</v>
       </c>
       <c r="I57" s="3">
-        <v>2533000</v>
+        <v>2305500</v>
       </c>
       <c r="J57" s="3">
+        <v>2525800</v>
+      </c>
+      <c r="K57" s="3">
         <v>2765700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2298400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1901800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1909600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1642500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1732400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1962600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1809700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1691000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2183800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2068800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2373000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2429800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2507100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2299400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2036400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>674500</v>
+        <v>772700</v>
       </c>
       <c r="E58" s="3">
-        <v>546800</v>
+        <v>672600</v>
       </c>
       <c r="F58" s="3">
-        <v>500000</v>
+        <v>545200</v>
       </c>
       <c r="G58" s="3">
-        <v>559600</v>
+        <v>498600</v>
       </c>
       <c r="H58" s="3">
-        <v>639900</v>
+        <v>558000</v>
       </c>
       <c r="I58" s="3">
-        <v>1051500</v>
+        <v>638100</v>
       </c>
       <c r="J58" s="3">
+        <v>1048500</v>
+      </c>
+      <c r="K58" s="3">
         <v>739500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>646800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>393700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>393500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>442200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>466400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>491800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>700500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>718600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>782800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>681500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>731100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>945500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1009000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1057500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>675900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>508300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>571600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>954700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>433200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>429200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>404800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1000700</v>
+        <v>762200</v>
       </c>
       <c r="E59" s="3">
-        <v>1052400</v>
+        <v>997800</v>
       </c>
       <c r="F59" s="3">
-        <v>910000</v>
+        <v>1049400</v>
       </c>
       <c r="G59" s="3">
-        <v>1018900</v>
+        <v>907400</v>
       </c>
       <c r="H59" s="3">
-        <v>1108600</v>
+        <v>1016000</v>
       </c>
       <c r="I59" s="3">
-        <v>1105400</v>
+        <v>1105500</v>
       </c>
       <c r="J59" s="3">
+        <v>1102300</v>
+      </c>
+      <c r="K59" s="3">
         <v>1017300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1146500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>663900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>488300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>379600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>554400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>370700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>376900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>483300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>535900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>492900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>426400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>529000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>684000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>603300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>509000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>526400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>410100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>337100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>411300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>458100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4163600</v>
+        <v>4045400</v>
       </c>
       <c r="E60" s="3">
-        <v>3957400</v>
+        <v>4151700</v>
       </c>
       <c r="F60" s="3">
-        <v>3831700</v>
+        <v>3946100</v>
       </c>
       <c r="G60" s="3">
-        <v>4016600</v>
+        <v>3820800</v>
       </c>
       <c r="H60" s="3">
-        <v>4060700</v>
+        <v>4005100</v>
       </c>
       <c r="I60" s="3">
-        <v>4690000</v>
+        <v>4049100</v>
       </c>
       <c r="J60" s="3">
+        <v>4676600</v>
+      </c>
+      <c r="K60" s="3">
         <v>4522500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4091700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2959400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2791300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2464300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2599200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3008800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2880900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2786600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3450000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3286200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3597000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3801800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4045200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4040900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3315500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2748900</v>
+        <v>2931900</v>
       </c>
       <c r="E61" s="3">
-        <v>2840500</v>
+        <v>2741000</v>
       </c>
       <c r="F61" s="3">
-        <v>2822700</v>
+        <v>2832400</v>
       </c>
       <c r="G61" s="3">
-        <v>2809300</v>
+        <v>2814600</v>
       </c>
       <c r="H61" s="3">
-        <v>2469100</v>
+        <v>2801300</v>
       </c>
       <c r="I61" s="3">
-        <v>1972100</v>
+        <v>2462100</v>
       </c>
       <c r="J61" s="3">
+        <v>1966500</v>
+      </c>
+      <c r="K61" s="3">
         <v>1997200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1927300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2398100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2310300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2225300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2347100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2569900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2620900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2694100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2156700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2087200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2405400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2153000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1195400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1054000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>806700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>959300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>948900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>356300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>368600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>415900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>550400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2505300</v>
+        <v>2612600</v>
       </c>
       <c r="E62" s="3">
-        <v>2452000</v>
+        <v>2498100</v>
       </c>
       <c r="F62" s="3">
-        <v>2515300</v>
+        <v>2445100</v>
       </c>
       <c r="G62" s="3">
-        <v>2379000</v>
+        <v>2508100</v>
       </c>
       <c r="H62" s="3">
-        <v>2085400</v>
+        <v>2372200</v>
       </c>
       <c r="I62" s="3">
-        <v>2229400</v>
+        <v>2079500</v>
       </c>
       <c r="J62" s="3">
+        <v>2223100</v>
+      </c>
+      <c r="K62" s="3">
         <v>2306000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2416100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2541500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2318000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3260900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3439400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3429000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3510900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3361000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3719000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3516400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3912800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3455400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3278400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3547300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2811300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10044200</v>
+        <v>10180800</v>
       </c>
       <c r="E66" s="3">
-        <v>9694400</v>
+        <v>10015600</v>
       </c>
       <c r="F66" s="3">
-        <v>9640900</v>
+        <v>9666800</v>
       </c>
       <c r="G66" s="3">
-        <v>9752800</v>
+        <v>9613500</v>
       </c>
       <c r="H66" s="3">
-        <v>9122000</v>
+        <v>9725100</v>
       </c>
       <c r="I66" s="3">
-        <v>9457500</v>
+        <v>9096100</v>
       </c>
       <c r="J66" s="3">
+        <v>9430600</v>
+      </c>
+      <c r="K66" s="3">
         <v>9365200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8947600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8220700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7761700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8228700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8679200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9335600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9322800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9168900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9726700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9348900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10441200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9925000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9051500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8925000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7391100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5774800</v>
+        <v>5867400</v>
       </c>
       <c r="E72" s="3">
-        <v>5964300</v>
+        <v>5758400</v>
       </c>
       <c r="F72" s="3">
-        <v>6013900</v>
+        <v>5947300</v>
       </c>
       <c r="G72" s="3">
-        <v>6777200</v>
+        <v>5996800</v>
       </c>
       <c r="H72" s="3">
-        <v>6674300</v>
+        <v>6757900</v>
       </c>
       <c r="I72" s="3">
-        <v>6632500</v>
+        <v>6655400</v>
       </c>
       <c r="J72" s="3">
+        <v>6613600</v>
+      </c>
+      <c r="K72" s="3">
         <v>6265000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6022700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4972300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4877400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5029300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5304700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5389100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5010800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5033300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5159600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5837800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6405600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6299500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6466900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6443600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5915000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9540800</v>
+        <v>9979400</v>
       </c>
       <c r="E76" s="3">
-        <v>9776600</v>
+        <v>9513700</v>
       </c>
       <c r="F76" s="3">
-        <v>10138000</v>
+        <v>9748700</v>
       </c>
       <c r="G76" s="3">
-        <v>10300100</v>
+        <v>10109100</v>
       </c>
       <c r="H76" s="3">
-        <v>9718900</v>
+        <v>10270800</v>
       </c>
       <c r="I76" s="3">
-        <v>10162300</v>
+        <v>9691200</v>
       </c>
       <c r="J76" s="3">
+        <v>10133300</v>
+      </c>
+      <c r="K76" s="3">
         <v>9424100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8588600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7292900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7328000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7030500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7415500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7693800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7479300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7661600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8429500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8847000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9661900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9382700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9587900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9682200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8492100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-240600</v>
+        <v>89000</v>
       </c>
       <c r="E81" s="3">
-        <v>-34000</v>
+        <v>-239900</v>
       </c>
       <c r="F81" s="3">
-        <v>494400</v>
+        <v>-33900</v>
       </c>
       <c r="G81" s="3">
-        <v>120000</v>
+        <v>493000</v>
       </c>
       <c r="H81" s="3">
-        <v>27200</v>
+        <v>119700</v>
       </c>
       <c r="I81" s="3">
-        <v>649900</v>
+        <v>27100</v>
       </c>
       <c r="J81" s="3">
+        <v>648000</v>
+      </c>
+      <c r="K81" s="3">
         <v>1069700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>524900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>670300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>94900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>243100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>143000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>531000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-22600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-126400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-183500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-52700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-151500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-78200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>76800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>215600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>226900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>405100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>235900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>171800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>217300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>130700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>660400</v>
+        <v>233800</v>
       </c>
       <c r="E83" s="3">
-        <v>220700</v>
+        <v>658500</v>
       </c>
       <c r="F83" s="3">
-        <v>222000</v>
+        <v>220100</v>
       </c>
       <c r="G83" s="3">
-        <v>207400</v>
+        <v>221300</v>
       </c>
       <c r="H83" s="3">
-        <v>242500</v>
+        <v>206800</v>
       </c>
       <c r="I83" s="3">
-        <v>207300</v>
+        <v>241800</v>
       </c>
       <c r="J83" s="3">
+        <v>206700</v>
+      </c>
+      <c r="K83" s="3">
         <v>205700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>184700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>226800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>197700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>178000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>186100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>415700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>211200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>400700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>222800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>337000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>269100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>243500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>237500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>193900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>189400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>193300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>207100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>228100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>168000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>160800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>166700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>197300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>296900</v>
+        <v>-7900</v>
       </c>
       <c r="E89" s="3">
-        <v>482600</v>
+        <v>296100</v>
       </c>
       <c r="F89" s="3">
-        <v>959000</v>
+        <v>481300</v>
       </c>
       <c r="G89" s="3">
-        <v>351400</v>
+        <v>956300</v>
       </c>
       <c r="H89" s="3">
-        <v>797700</v>
+        <v>350400</v>
       </c>
       <c r="I89" s="3">
-        <v>570800</v>
+        <v>795400</v>
       </c>
       <c r="J89" s="3">
+        <v>569100</v>
+      </c>
+      <c r="K89" s="3">
         <v>1432200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>791900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>615000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-54000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>563900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>457800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>221800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>138000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>628700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>420200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>300600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>88200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>106500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>263300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>155300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>215800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>740900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>341600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>501400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>82400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>523700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3078000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4329000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3200000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3476000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2633000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-182900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-127700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-116400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-136900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-320200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-237200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-258000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-184600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-284000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-183700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-508400</v>
+        <v>-534700</v>
       </c>
       <c r="E94" s="3">
-        <v>-714600</v>
+        <v>-507000</v>
       </c>
       <c r="F94" s="3">
-        <v>-450900</v>
+        <v>-712500</v>
       </c>
       <c r="G94" s="3">
-        <v>-295300</v>
+        <v>-449600</v>
       </c>
       <c r="H94" s="3">
-        <v>-401600</v>
+        <v>-294500</v>
       </c>
       <c r="I94" s="3">
-        <v>-394600</v>
+        <v>-400500</v>
       </c>
       <c r="J94" s="3">
+        <v>-393500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-45700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-154100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-265300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-138800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>85700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-128800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>12700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-131700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-456900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-194500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-324000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-234000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-310700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-182800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-292200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-154800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>220100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8130,41 +8364,41 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-1192800</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-1189400</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-11300</v>
       </c>
-      <c r="I96" s="3">
-        <v>-282300</v>
-      </c>
       <c r="J96" s="3">
+        <v>-281500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-24300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-241200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-272200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8172,49 +8406,52 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-10100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-295800</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>806700</v>
+        <v>8300</v>
       </c>
       <c r="E100" s="3">
-        <v>-42900</v>
+        <v>804400</v>
       </c>
       <c r="F100" s="3">
-        <v>-1362900</v>
+        <v>-42800</v>
       </c>
       <c r="G100" s="3">
-        <v>-36500</v>
+        <v>-1359000</v>
       </c>
       <c r="H100" s="3">
-        <v>22100</v>
+        <v>-36400</v>
       </c>
       <c r="I100" s="3">
-        <v>-118400</v>
+        <v>22000</v>
       </c>
       <c r="J100" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-151900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>38200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-250200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-49300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-493200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-73900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>669000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-107400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-208300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>531200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>115200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>45700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>22200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>101800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>602000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>26000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-72200</v>
+        <v>61700</v>
       </c>
       <c r="E101" s="3">
-        <v>-42800</v>
+        <v>-72000</v>
       </c>
       <c r="F101" s="3">
-        <v>56000</v>
+        <v>-42700</v>
       </c>
       <c r="G101" s="3">
-        <v>81800</v>
+        <v>55800</v>
       </c>
       <c r="H101" s="3">
-        <v>-43200</v>
+        <v>81500</v>
       </c>
       <c r="I101" s="3">
-        <v>69800</v>
+        <v>-43000</v>
       </c>
       <c r="J101" s="3">
+        <v>69600</v>
+      </c>
+      <c r="K101" s="3">
         <v>76900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>23900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>13900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-19000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>32500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-28500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-22300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-95400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>58500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-8600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>21100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-8800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>44000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-11700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>31000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>9000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>30300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>523000</v>
+        <v>-472600</v>
       </c>
       <c r="E102" s="3">
-        <v>-317600</v>
+        <v>521500</v>
       </c>
       <c r="F102" s="3">
-        <v>-798700</v>
+        <v>-316700</v>
       </c>
       <c r="G102" s="3">
-        <v>101300</v>
+        <v>-796400</v>
       </c>
       <c r="H102" s="3">
-        <v>375000</v>
+        <v>101000</v>
       </c>
       <c r="I102" s="3">
-        <v>127600</v>
+        <v>373900</v>
       </c>
       <c r="J102" s="3">
+        <v>127200</v>
+      </c>
+      <c r="K102" s="3">
         <v>317400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-161200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>388600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-127500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>483000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-260500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>14800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>213700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>326700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>188700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>519300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>11800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-96000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>119100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>36500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>10500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-156300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4497300</v>
+        <v>4790800</v>
       </c>
       <c r="E8" s="3">
-        <v>4422500</v>
+        <v>4471100</v>
       </c>
       <c r="F8" s="3">
-        <v>4228400</v>
+        <v>4396700</v>
       </c>
       <c r="G8" s="3">
-        <v>5072900</v>
+        <v>4203800</v>
       </c>
       <c r="H8" s="3">
-        <v>4590800</v>
+        <v>5043400</v>
       </c>
       <c r="I8" s="3">
-        <v>4169100</v>
+        <v>4564100</v>
       </c>
       <c r="J8" s="3">
+        <v>4144800</v>
+      </c>
+      <c r="K8" s="3">
         <v>4960800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6146300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4263500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4367500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3452900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3250600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3169900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1249900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2787400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2567200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3202000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3928000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4515500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4529900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4254800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4330700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2840100</v>
+        <v>3141900</v>
       </c>
       <c r="E9" s="3">
-        <v>2803000</v>
+        <v>2823600</v>
       </c>
       <c r="F9" s="3">
-        <v>2885100</v>
+        <v>2786700</v>
       </c>
       <c r="G9" s="3">
-        <v>3037200</v>
+        <v>2868300</v>
       </c>
       <c r="H9" s="3">
-        <v>2960200</v>
+        <v>3019500</v>
       </c>
       <c r="I9" s="3">
-        <v>2729600</v>
+        <v>2943000</v>
       </c>
       <c r="J9" s="3">
+        <v>2713700</v>
+      </c>
+      <c r="K9" s="3">
         <v>3246800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3512800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2667000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2333100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2229300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1995300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1897500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>625800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1676100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1603700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1894400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2471300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2899500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2997100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2845600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2839000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2625700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1657200</v>
+        <v>1648900</v>
       </c>
       <c r="E10" s="3">
-        <v>1619500</v>
+        <v>1647600</v>
       </c>
       <c r="F10" s="3">
-        <v>1343300</v>
+        <v>1610100</v>
       </c>
       <c r="G10" s="3">
-        <v>2035700</v>
+        <v>1335500</v>
       </c>
       <c r="H10" s="3">
-        <v>1630600</v>
+        <v>2023800</v>
       </c>
       <c r="I10" s="3">
-        <v>1439500</v>
+        <v>1621200</v>
       </c>
       <c r="J10" s="3">
+        <v>1431100</v>
+      </c>
+      <c r="K10" s="3">
         <v>1714000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2633500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1596500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2034400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1223600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1255300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1272400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>624100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1111300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>963600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1307600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1456800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1616100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1532800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1409100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1491700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1442300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>929900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>969000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,67 +1338,70 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E14" s="3">
-        <v>418500</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>416000</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-300</v>
       </c>
-      <c r="I14" s="3">
-        <v>27100</v>
-      </c>
       <c r="J14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K14" s="3">
         <v>4600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>27700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>185300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100900</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1398,11 +1418,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1419,106 +1439,112 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>233800</v>
+        <v>234900</v>
       </c>
       <c r="E15" s="3">
-        <v>240100</v>
+        <v>232500</v>
       </c>
       <c r="F15" s="3">
+        <v>238700</v>
+      </c>
+      <c r="G15" s="3">
+        <v>218800</v>
+      </c>
+      <c r="H15" s="3">
         <v>220100</v>
       </c>
-      <c r="G15" s="3">
-        <v>221300</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>205900</v>
+      </c>
+      <c r="J15" s="3">
+        <v>213500</v>
+      </c>
+      <c r="K15" s="3">
+        <v>202000</v>
+      </c>
+      <c r="L15" s="3">
+        <v>205600</v>
+      </c>
+      <c r="M15" s="3">
+        <v>184700</v>
+      </c>
+      <c r="N15" s="3">
+        <v>199100</v>
+      </c>
+      <c r="O15" s="3">
+        <v>196400</v>
+      </c>
+      <c r="P15" s="3">
+        <v>177300</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>174000</v>
+      </c>
+      <c r="R15" s="3">
+        <v>88100</v>
+      </c>
+      <c r="S15" s="3">
+        <v>173300</v>
+      </c>
+      <c r="T15" s="3">
+        <v>184400</v>
+      </c>
+      <c r="U15" s="3">
+        <v>192100</v>
+      </c>
+      <c r="V15" s="3">
+        <v>236000</v>
+      </c>
+      <c r="W15" s="3">
+        <v>269100</v>
+      </c>
+      <c r="X15" s="3">
+        <v>243400</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>237500</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>193900</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>189400</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>193400</v>
+      </c>
+      <c r="AC15" s="3">
         <v>207100</v>
       </c>
-      <c r="I15" s="3">
-        <v>214700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>202000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>205600</v>
-      </c>
-      <c r="L15" s="3">
-        <v>184700</v>
-      </c>
-      <c r="M15" s="3">
-        <v>199100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>196400</v>
-      </c>
-      <c r="O15" s="3">
-        <v>177300</v>
-      </c>
-      <c r="P15" s="3">
-        <v>174000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>88100</v>
-      </c>
-      <c r="R15" s="3">
-        <v>173300</v>
-      </c>
-      <c r="S15" s="3">
-        <v>184400</v>
-      </c>
-      <c r="T15" s="3">
-        <v>192100</v>
-      </c>
-      <c r="U15" s="3">
-        <v>236000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>269100</v>
-      </c>
-      <c r="W15" s="3">
-        <v>243400</v>
-      </c>
-      <c r="X15" s="3">
-        <v>237500</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>193900</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>189400</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>193400</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>207100</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>228100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>167900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>160800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>166700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>197200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4207300</v>
+        <v>4456300</v>
       </c>
       <c r="E17" s="3">
-        <v>4636000</v>
+        <v>4182800</v>
       </c>
       <c r="F17" s="3">
-        <v>4258900</v>
+        <v>4609000</v>
       </c>
       <c r="G17" s="3">
-        <v>4321900</v>
+        <v>4234200</v>
       </c>
       <c r="H17" s="3">
-        <v>4190400</v>
+        <v>4296800</v>
       </c>
       <c r="I17" s="3">
-        <v>4036200</v>
+        <v>4166100</v>
       </c>
       <c r="J17" s="3">
+        <v>4012700</v>
+      </c>
+      <c r="K17" s="3">
         <v>4235300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4683700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3694400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3418800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3214700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2965200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2948300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>535800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2595600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2728100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2976300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3972200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4488800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4454100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4252500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4310600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3857600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>290000</v>
+        <v>334500</v>
       </c>
       <c r="E18" s="3">
-        <v>-213500</v>
+        <v>288300</v>
       </c>
       <c r="F18" s="3">
-        <v>-30600</v>
+        <v>-212200</v>
       </c>
       <c r="G18" s="3">
-        <v>751000</v>
+        <v>-30400</v>
       </c>
       <c r="H18" s="3">
-        <v>400400</v>
+        <v>746600</v>
       </c>
       <c r="I18" s="3">
-        <v>132900</v>
+        <v>398100</v>
       </c>
       <c r="J18" s="3">
+        <v>132100</v>
+      </c>
+      <c r="K18" s="3">
         <v>725500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1462600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>569100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>948700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>238300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>285400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>221500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>714100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>191800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-160900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>225700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-44200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>26700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>75900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>210400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>305500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>358100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>522300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>269000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>341100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>297200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>242200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-125000</v>
+        <v>-56600</v>
       </c>
       <c r="E20" s="3">
-        <v>31600</v>
+        <v>-124200</v>
       </c>
       <c r="F20" s="3">
-        <v>83900</v>
+        <v>31400</v>
       </c>
       <c r="G20" s="3">
-        <v>-45000</v>
+        <v>83400</v>
       </c>
       <c r="H20" s="3">
-        <v>-164200</v>
+        <v>-44800</v>
       </c>
       <c r="I20" s="3">
-        <v>54400</v>
+        <v>-163300</v>
       </c>
       <c r="J20" s="3">
+        <v>54100</v>
+      </c>
+      <c r="K20" s="3">
         <v>72400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-96300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>221000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>83700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-62000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>54000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>65600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>184400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-152000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>62700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-426500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>52700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-170700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-51800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>20800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-51000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-27200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>60900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>27100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>398900</v>
+        <v>514400</v>
       </c>
       <c r="E21" s="3">
-        <v>476600</v>
+        <v>396600</v>
       </c>
       <c r="F21" s="3">
-        <v>273500</v>
+        <v>473900</v>
       </c>
       <c r="G21" s="3">
-        <v>927300</v>
+        <v>271900</v>
       </c>
       <c r="H21" s="3">
-        <v>443000</v>
+        <v>921900</v>
       </c>
       <c r="I21" s="3">
-        <v>429100</v>
+        <v>440400</v>
       </c>
       <c r="J21" s="3">
+        <v>426600</v>
+      </c>
+      <c r="K21" s="3">
         <v>1004500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1571900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>974800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1259200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>374000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>517300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>473200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1085900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>220600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>271500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>345500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>125200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>267600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>260600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>163000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>372600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>468800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>527000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>673000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>497900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>399100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>491000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>435600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>56500</v>
+        <v>74800</v>
       </c>
       <c r="E22" s="3">
         <v>56100</v>
       </c>
       <c r="F22" s="3">
-        <v>48100</v>
+        <v>55800</v>
       </c>
       <c r="G22" s="3">
-        <v>45100</v>
+        <v>47900</v>
       </c>
       <c r="H22" s="3">
-        <v>45000</v>
+        <v>44900</v>
       </c>
       <c r="I22" s="3">
-        <v>28800</v>
+        <v>44800</v>
       </c>
       <c r="J22" s="3">
+        <v>28600</v>
+      </c>
+      <c r="K22" s="3">
         <v>25400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>26200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>26400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>22100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>27000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>25400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>25000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>30300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>13300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>13400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>108600</v>
+        <v>203100</v>
       </c>
       <c r="E23" s="3">
-        <v>-238000</v>
+        <v>108000</v>
       </c>
       <c r="F23" s="3">
+        <v>-236600</v>
+      </c>
+      <c r="G23" s="3">
         <v>5200</v>
       </c>
-      <c r="G23" s="3">
-        <v>660800</v>
-      </c>
       <c r="H23" s="3">
-        <v>191200</v>
+        <v>657000</v>
       </c>
       <c r="I23" s="3">
-        <v>158500</v>
+        <v>190100</v>
       </c>
       <c r="J23" s="3">
+        <v>157600</v>
+      </c>
+      <c r="K23" s="3">
         <v>772400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1338300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>769700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1009300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>152400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>318800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>263600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>872200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-121600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-222900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-18500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-169300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-61300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>167200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>260400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>306600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>432500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>325100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>230100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>313900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>224900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>68100</v>
+        <v>69500</v>
       </c>
       <c r="E24" s="3">
-        <v>24200</v>
+        <v>67700</v>
       </c>
       <c r="F24" s="3">
-        <v>64300</v>
+        <v>24100</v>
       </c>
       <c r="G24" s="3">
-        <v>182600</v>
+        <v>63900</v>
       </c>
       <c r="H24" s="3">
-        <v>83000</v>
+        <v>181500</v>
       </c>
       <c r="I24" s="3">
-        <v>143700</v>
+        <v>82500</v>
       </c>
       <c r="J24" s="3">
+        <v>142800</v>
+      </c>
+      <c r="K24" s="3">
         <v>140800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>281800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>183400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>207400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>93300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>77000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>84700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>24500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>29100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-46300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>55000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>17000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>23500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>72600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>48400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>81300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>15600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>72300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>49100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>87200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>40500</v>
+        <v>133600</v>
       </c>
       <c r="E26" s="3">
-        <v>-262200</v>
+        <v>40200</v>
       </c>
       <c r="F26" s="3">
-        <v>-59100</v>
+        <v>-260700</v>
       </c>
       <c r="G26" s="3">
-        <v>478200</v>
+        <v>-58800</v>
       </c>
       <c r="H26" s="3">
-        <v>108200</v>
+        <v>475500</v>
       </c>
       <c r="I26" s="3">
-        <v>14900</v>
+        <v>107600</v>
       </c>
       <c r="J26" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K26" s="3">
         <v>631600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1056500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>586400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>801900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>105900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>225500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>186600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>787500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-150600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-176600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-73500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-167400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-22100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-84700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>94500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>212000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>225300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>416800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>252900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>181000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>226700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>124400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>89000</v>
+        <v>201600</v>
       </c>
       <c r="E27" s="3">
-        <v>-239900</v>
+        <v>88500</v>
       </c>
       <c r="F27" s="3">
-        <v>-33900</v>
+        <v>-238500</v>
       </c>
       <c r="G27" s="3">
-        <v>493000</v>
+        <v>-33700</v>
       </c>
       <c r="H27" s="3">
-        <v>119700</v>
+        <v>490100</v>
       </c>
       <c r="I27" s="3">
-        <v>23700</v>
+        <v>119000</v>
       </c>
       <c r="J27" s="3">
+        <v>23600</v>
+      </c>
+      <c r="K27" s="3">
         <v>648000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1069700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>524900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>669900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>96700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>204900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>180700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>761500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-128000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-154900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-52700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-151500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-78200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>76800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>215600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>226900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>405100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>235900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>171800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>217300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>130700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,16 +2722,19 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2685,11 +2746,11 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>3400</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -2697,37 +2758,37 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>38300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-230600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-11200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>1600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-28600</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>125000</v>
+        <v>56600</v>
       </c>
       <c r="E32" s="3">
-        <v>-31600</v>
+        <v>124200</v>
       </c>
       <c r="F32" s="3">
-        <v>-83900</v>
+        <v>-31400</v>
       </c>
       <c r="G32" s="3">
-        <v>45000</v>
+        <v>-83400</v>
       </c>
       <c r="H32" s="3">
-        <v>164200</v>
+        <v>44800</v>
       </c>
       <c r="I32" s="3">
-        <v>-54400</v>
+        <v>163300</v>
       </c>
       <c r="J32" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-72400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>96300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-221000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-83700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>62000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-54000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-65600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-184400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>152000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-62700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>426500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-52700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>170700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>51800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-20800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>51000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>27200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>30000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>38200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>77500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>102800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>89000</v>
+        <v>201600</v>
       </c>
       <c r="E33" s="3">
-        <v>-239900</v>
+        <v>88500</v>
       </c>
       <c r="F33" s="3">
-        <v>-33900</v>
+        <v>-238500</v>
       </c>
       <c r="G33" s="3">
-        <v>493000</v>
+        <v>-33700</v>
       </c>
       <c r="H33" s="3">
-        <v>119700</v>
+        <v>490100</v>
       </c>
       <c r="I33" s="3">
-        <v>27100</v>
+        <v>119000</v>
       </c>
       <c r="J33" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K33" s="3">
         <v>648000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1069700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>524900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>670300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>94900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>243100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>143000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>531000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-22600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-126400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-183500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-52700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-151500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-78200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>76800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>215600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>226900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>405100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>235900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>171800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>217300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>130700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>89000</v>
+        <v>201600</v>
       </c>
       <c r="E35" s="3">
-        <v>-239900</v>
+        <v>88500</v>
       </c>
       <c r="F35" s="3">
-        <v>-33900</v>
+        <v>-238500</v>
       </c>
       <c r="G35" s="3">
-        <v>493000</v>
+        <v>-33700</v>
       </c>
       <c r="H35" s="3">
-        <v>119700</v>
+        <v>490100</v>
       </c>
       <c r="I35" s="3">
-        <v>27100</v>
+        <v>119000</v>
       </c>
       <c r="J35" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K35" s="3">
         <v>648000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1069700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>524900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>670300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>94900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>243100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>143000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>531000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-22600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-126400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-183500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-52700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-151500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-78200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>76800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>215600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>226900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>405100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>235900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>171800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>217300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>130700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,204 +3611,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1856000</v>
+        <v>1776000</v>
       </c>
       <c r="E41" s="3">
-        <v>2328600</v>
+        <v>1845300</v>
       </c>
       <c r="F41" s="3">
-        <v>1807100</v>
+        <v>2315100</v>
       </c>
       <c r="G41" s="3">
-        <v>2123800</v>
+        <v>1796600</v>
       </c>
       <c r="H41" s="3">
-        <v>2920300</v>
+        <v>2111500</v>
       </c>
       <c r="I41" s="3">
-        <v>2819300</v>
+        <v>2903300</v>
       </c>
       <c r="J41" s="3">
+        <v>2802900</v>
+      </c>
+      <c r="K41" s="3">
         <v>2445300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2324700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1935400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1767600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1895000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1411900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1489200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1826900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1772200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1558500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1231800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1359800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1273500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1224500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>690500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>676400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>700300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>581300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>925500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>991000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>597600</v>
+        <v>443100</v>
       </c>
       <c r="E42" s="3">
-        <v>429500</v>
+        <v>594100</v>
       </c>
       <c r="F42" s="3">
-        <v>362000</v>
+        <v>427000</v>
       </c>
       <c r="G42" s="3">
-        <v>367000</v>
+        <v>359900</v>
       </c>
       <c r="H42" s="3">
-        <v>378200</v>
+        <v>364900</v>
       </c>
       <c r="I42" s="3">
-        <v>501300</v>
+        <v>376000</v>
       </c>
       <c r="J42" s="3">
+        <v>498400</v>
+      </c>
+      <c r="K42" s="3">
         <v>699800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>799200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1217100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>740600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>401300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>439800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>463900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>472400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>602900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>587200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>279600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>177500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>196100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>180500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>183700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>200400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>195800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>216300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>200600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>244200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>259400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>600500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>580000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>624900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3769,156 +3862,162 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>2053100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1916200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2485800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2098400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2769100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2681000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2665200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2340300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2222700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2392300</v>
+        <v>2370600</v>
       </c>
       <c r="E44" s="3">
-        <v>2407200</v>
+        <v>2378400</v>
       </c>
       <c r="F44" s="3">
-        <v>2615200</v>
+        <v>2393200</v>
       </c>
       <c r="G44" s="3">
-        <v>2724900</v>
+        <v>2600000</v>
       </c>
       <c r="H44" s="3">
-        <v>2858100</v>
+        <v>2709100</v>
       </c>
       <c r="I44" s="3">
-        <v>2841000</v>
+        <v>2841500</v>
       </c>
       <c r="J44" s="3">
+        <v>2824500</v>
+      </c>
+      <c r="K44" s="3">
         <v>2969600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2790300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2308200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1783900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1547700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1346600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1420300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2019000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1953900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2064700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2275600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2303900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2609300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2626900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2830700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2987800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2446600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3934,11 +4033,11 @@
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
@@ -3964,11 +4063,11 @@
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>8</v>
@@ -3976,11 +4075,11 @@
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
@@ -3997,8 +4096,8 @@
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -4006,409 +4105,424 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-      <c r="AF45" s="3" t="s">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>100</v>
       </c>
-      <c r="AH45" s="3" t="s">
+      <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7586100</v>
+        <v>7287500</v>
       </c>
       <c r="E46" s="3">
-        <v>7568300</v>
+        <v>7542000</v>
       </c>
       <c r="F46" s="3">
-        <v>7280300</v>
+        <v>7524300</v>
       </c>
       <c r="G46" s="3">
-        <v>7822800</v>
+        <v>7238000</v>
       </c>
       <c r="H46" s="3">
-        <v>8838300</v>
+        <v>7777300</v>
       </c>
       <c r="I46" s="3">
-        <v>8430600</v>
+        <v>8786900</v>
       </c>
       <c r="J46" s="3">
+        <v>8381600</v>
+      </c>
+      <c r="K46" s="3">
         <v>8805000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8680700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7834500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6161000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5709900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4778100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5039700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6220500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6382300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6126600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6272800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5939600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6848100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6712900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6370100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6204900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5565400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2129400</v>
+        <v>2338900</v>
       </c>
       <c r="E47" s="3">
-        <v>2008000</v>
+        <v>2117000</v>
       </c>
       <c r="F47" s="3">
-        <v>2330000</v>
+        <v>1996300</v>
       </c>
       <c r="G47" s="3">
-        <v>2296400</v>
+        <v>2316500</v>
       </c>
       <c r="H47" s="3">
-        <v>2134500</v>
+        <v>2283000</v>
       </c>
       <c r="I47" s="3">
-        <v>2007400</v>
+        <v>2122100</v>
       </c>
       <c r="J47" s="3">
+        <v>1995700</v>
+      </c>
+      <c r="K47" s="3">
         <v>2139000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1902400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1669800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1661200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1639100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1620400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1709100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1790700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1220500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1278300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1402500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1272900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1421300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1264500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1284800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1305300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1134900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7315000</v>
+        <v>7001100</v>
       </c>
       <c r="E48" s="3">
-        <v>7092500</v>
+        <v>7272500</v>
       </c>
       <c r="F48" s="3">
-        <v>7034400</v>
+        <v>7051200</v>
       </c>
       <c r="G48" s="3">
-        <v>6903700</v>
+        <v>6993500</v>
       </c>
       <c r="H48" s="3">
-        <v>6415800</v>
+        <v>6863500</v>
       </c>
       <c r="I48" s="3">
-        <v>5926600</v>
+        <v>6378500</v>
       </c>
       <c r="J48" s="3">
+        <v>5892200</v>
+      </c>
+      <c r="K48" s="3">
         <v>5899500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5589200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5176500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5139600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5300600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5068900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5346400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6654500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6955000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7139400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7892200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8217200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8909600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8463300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8251000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8390300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6777500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>826800</v>
+        <v>786600</v>
       </c>
       <c r="E49" s="3">
-        <v>799000</v>
+        <v>822000</v>
       </c>
       <c r="F49" s="3">
-        <v>1023700</v>
+        <v>794400</v>
       </c>
       <c r="G49" s="3">
-        <v>966200</v>
+        <v>1017800</v>
       </c>
       <c r="H49" s="3">
-        <v>930700</v>
+        <v>960600</v>
       </c>
       <c r="I49" s="3">
-        <v>877800</v>
+        <v>925300</v>
       </c>
       <c r="J49" s="3">
+        <v>872700</v>
+      </c>
+      <c r="K49" s="3">
         <v>927900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>889200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>821900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>832600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>862900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>827400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>872700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>969200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1003200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1039500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1281300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1272900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1407600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1328000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1260400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1291000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1094100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>628400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>645800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>729800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>716500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2302900</v>
+        <v>1884100</v>
       </c>
       <c r="E52" s="3">
-        <v>2061500</v>
+        <v>2289500</v>
       </c>
       <c r="F52" s="3">
-        <v>1747100</v>
+        <v>2049500</v>
       </c>
       <c r="G52" s="3">
-        <v>1733600</v>
+        <v>1736900</v>
       </c>
       <c r="H52" s="3">
-        <v>1676600</v>
+        <v>1723500</v>
       </c>
       <c r="I52" s="3">
-        <v>1544800</v>
+        <v>1666900</v>
       </c>
       <c r="J52" s="3">
+        <v>1535900</v>
+      </c>
+      <c r="K52" s="3">
         <v>1792600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1727800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2033600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1719200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1577300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2964500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3126800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1394500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1241200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1246600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1307400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1493200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1516400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1538900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1473100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1415700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1311300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>20160300</v>
+        <v>19298200</v>
       </c>
       <c r="E54" s="3">
-        <v>19529200</v>
+        <v>20043000</v>
       </c>
       <c r="F54" s="3">
-        <v>19415500</v>
+        <v>19415700</v>
       </c>
       <c r="G54" s="3">
-        <v>19722600</v>
+        <v>19302700</v>
       </c>
       <c r="H54" s="3">
-        <v>19995900</v>
+        <v>19607900</v>
       </c>
       <c r="I54" s="3">
-        <v>18787300</v>
+        <v>19879600</v>
       </c>
       <c r="J54" s="3">
+        <v>18678000</v>
+      </c>
+      <c r="K54" s="3">
         <v>19564000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18789300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17536300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15513700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15089800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15259200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16094600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17029400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16802100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16830500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18156200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18195900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>20103100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>19307700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18639300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18607200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15883200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2510500</v>
+        <v>2476600</v>
       </c>
       <c r="E57" s="3">
-        <v>2481300</v>
+        <v>2495900</v>
       </c>
       <c r="F57" s="3">
-        <v>2351500</v>
+        <v>2466900</v>
       </c>
       <c r="G57" s="3">
-        <v>2414800</v>
+        <v>2337800</v>
       </c>
       <c r="H57" s="3">
-        <v>2431200</v>
+        <v>2400700</v>
       </c>
       <c r="I57" s="3">
-        <v>2305500</v>
+        <v>2417000</v>
       </c>
       <c r="J57" s="3">
+        <v>2292100</v>
+      </c>
+      <c r="K57" s="3">
         <v>2525800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2765700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2298400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1901800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1909600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1642500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1732400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1962600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1809700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1691000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2183800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2068800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2373000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2429800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2507100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2299400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2036400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>772700</v>
+        <v>1528100</v>
       </c>
       <c r="E58" s="3">
-        <v>672600</v>
+        <v>768200</v>
       </c>
       <c r="F58" s="3">
-        <v>545200</v>
+        <v>668700</v>
       </c>
       <c r="G58" s="3">
-        <v>498600</v>
+        <v>542000</v>
       </c>
       <c r="H58" s="3">
-        <v>558000</v>
+        <v>495700</v>
       </c>
       <c r="I58" s="3">
-        <v>638100</v>
+        <v>554700</v>
       </c>
       <c r="J58" s="3">
+        <v>634400</v>
+      </c>
+      <c r="K58" s="3">
         <v>1048500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>739500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>646800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>393700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>393500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>442200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>466400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>491800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>700500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>718600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>782800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>681500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>731100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>945500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1009000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1057500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>675900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>508300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>571600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>954700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>433200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>429200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>404800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>762200</v>
+        <v>805200</v>
       </c>
       <c r="E59" s="3">
-        <v>997800</v>
+        <v>757800</v>
       </c>
       <c r="F59" s="3">
-        <v>1049400</v>
+        <v>992000</v>
       </c>
       <c r="G59" s="3">
-        <v>907400</v>
+        <v>1043300</v>
       </c>
       <c r="H59" s="3">
-        <v>1016000</v>
+        <v>902100</v>
       </c>
       <c r="I59" s="3">
-        <v>1105500</v>
+        <v>1010100</v>
       </c>
       <c r="J59" s="3">
+        <v>1099000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1102300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1017300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1146500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>663900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>488300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>379600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>400400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>554400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>370700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>376900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>483300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>535900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>492900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>426400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>529000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>684000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>603300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>509000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>526400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>410100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>337100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>411300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>458100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4045400</v>
+        <v>4809900</v>
       </c>
       <c r="E60" s="3">
-        <v>4151700</v>
+        <v>4021900</v>
       </c>
       <c r="F60" s="3">
-        <v>3946100</v>
+        <v>4127600</v>
       </c>
       <c r="G60" s="3">
-        <v>3820800</v>
+        <v>3923200</v>
       </c>
       <c r="H60" s="3">
-        <v>4005100</v>
+        <v>3798600</v>
       </c>
       <c r="I60" s="3">
-        <v>4049100</v>
+        <v>3981800</v>
       </c>
       <c r="J60" s="3">
+        <v>4025600</v>
+      </c>
+      <c r="K60" s="3">
         <v>4676600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4522500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4091700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2959400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2791300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2464300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2599200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3008800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2880900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2786600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3450000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3286200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3597000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3801800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4045200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4040900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3315500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2931900</v>
+        <v>2150400</v>
       </c>
       <c r="E61" s="3">
-        <v>2741000</v>
+        <v>2914900</v>
       </c>
       <c r="F61" s="3">
-        <v>2832400</v>
+        <v>2725100</v>
       </c>
       <c r="G61" s="3">
-        <v>2814600</v>
+        <v>2815900</v>
       </c>
       <c r="H61" s="3">
-        <v>2801300</v>
+        <v>2798300</v>
       </c>
       <c r="I61" s="3">
-        <v>2462100</v>
+        <v>2785000</v>
       </c>
       <c r="J61" s="3">
+        <v>2447800</v>
+      </c>
+      <c r="K61" s="3">
         <v>1966500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1997200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1927300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2398100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2310300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2225300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2347100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2569900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2620900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2694100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2156700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2087200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2405400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2153000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1195400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1054000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>806700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>959300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>948900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>356300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>368600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>415900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>550400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2612600</v>
+        <v>2572700</v>
       </c>
       <c r="E62" s="3">
-        <v>2498100</v>
+        <v>2597400</v>
       </c>
       <c r="F62" s="3">
-        <v>2445100</v>
+        <v>2483600</v>
       </c>
       <c r="G62" s="3">
-        <v>2508100</v>
+        <v>2430800</v>
       </c>
       <c r="H62" s="3">
-        <v>2372200</v>
+        <v>2493600</v>
       </c>
       <c r="I62" s="3">
-        <v>2079500</v>
+        <v>2358400</v>
       </c>
       <c r="J62" s="3">
+        <v>2067400</v>
+      </c>
+      <c r="K62" s="3">
         <v>2223100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2306000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2416100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2541500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2318000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3260900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3439400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3429000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3510900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3361000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3719000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3516400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3912800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3455400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3278400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3547300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2811300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10180800</v>
+        <v>10040200</v>
       </c>
       <c r="E66" s="3">
-        <v>10015600</v>
+        <v>10121600</v>
       </c>
       <c r="F66" s="3">
-        <v>9666800</v>
+        <v>9957300</v>
       </c>
       <c r="G66" s="3">
-        <v>9613500</v>
+        <v>9610600</v>
       </c>
       <c r="H66" s="3">
-        <v>9725100</v>
+        <v>9557600</v>
       </c>
       <c r="I66" s="3">
-        <v>9096100</v>
+        <v>9668500</v>
       </c>
       <c r="J66" s="3">
+        <v>9043200</v>
+      </c>
+      <c r="K66" s="3">
         <v>9430600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9365200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8947600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8220700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7761700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8228700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8679200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9335600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9322800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9168900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9726700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9348900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10441200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9925000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9051500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8925000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7391100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5867400</v>
+        <v>5359000</v>
       </c>
       <c r="E72" s="3">
-        <v>5758400</v>
+        <v>5833300</v>
       </c>
       <c r="F72" s="3">
-        <v>5947300</v>
+        <v>5724900</v>
       </c>
       <c r="G72" s="3">
-        <v>5996800</v>
+        <v>5912800</v>
       </c>
       <c r="H72" s="3">
-        <v>6757900</v>
+        <v>5961900</v>
       </c>
       <c r="I72" s="3">
-        <v>6655400</v>
+        <v>6718600</v>
       </c>
       <c r="J72" s="3">
+        <v>6616700</v>
+      </c>
+      <c r="K72" s="3">
         <v>6613600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6265000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6022700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4972300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4877400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5029300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5304700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5389100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5010800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5033300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5159600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5837800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6405600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6299500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6466900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6443600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5915000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9979400</v>
+        <v>9258000</v>
       </c>
       <c r="E76" s="3">
-        <v>9513700</v>
+        <v>9921400</v>
       </c>
       <c r="F76" s="3">
-        <v>9748700</v>
+        <v>9458400</v>
       </c>
       <c r="G76" s="3">
-        <v>10109100</v>
+        <v>9692000</v>
       </c>
       <c r="H76" s="3">
-        <v>10270800</v>
+        <v>10050300</v>
       </c>
       <c r="I76" s="3">
-        <v>9691200</v>
+        <v>10211100</v>
       </c>
       <c r="J76" s="3">
+        <v>9634900</v>
+      </c>
+      <c r="K76" s="3">
         <v>10133300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9424100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8588600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7292900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7328000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7030500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7415500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7693800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7479300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7661600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8429500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8847000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9661900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9382700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9587900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9682200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8492100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>89000</v>
+        <v>201600</v>
       </c>
       <c r="E81" s="3">
-        <v>-239900</v>
+        <v>88500</v>
       </c>
       <c r="F81" s="3">
-        <v>-33900</v>
+        <v>-238500</v>
       </c>
       <c r="G81" s="3">
-        <v>493000</v>
+        <v>-33700</v>
       </c>
       <c r="H81" s="3">
-        <v>119700</v>
+        <v>490100</v>
       </c>
       <c r="I81" s="3">
-        <v>27100</v>
+        <v>119000</v>
       </c>
       <c r="J81" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K81" s="3">
         <v>648000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1069700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>524900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>670300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>94900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>243100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>143000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>531000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-22600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-126400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-183500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-52700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-151500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-78200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>76800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>215600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>226900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>405100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>235900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>171800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>217300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>130700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>233800</v>
+        <v>236500</v>
       </c>
       <c r="E83" s="3">
-        <v>658500</v>
+        <v>232500</v>
       </c>
       <c r="F83" s="3">
+        <v>654700</v>
+      </c>
+      <c r="G83" s="3">
+        <v>218800</v>
+      </c>
+      <c r="H83" s="3">
         <v>220100</v>
       </c>
-      <c r="G83" s="3">
-        <v>221300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>206800</v>
-      </c>
       <c r="I83" s="3">
-        <v>241800</v>
+        <v>205600</v>
       </c>
       <c r="J83" s="3">
+        <v>240400</v>
+      </c>
+      <c r="K83" s="3">
         <v>206700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>205700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>184700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>226800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>197700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>178000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>186100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>415700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>211200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>400700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>222800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>337000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>269100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>243500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>237500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>193900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>189400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>193300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>207100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>228100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>168000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>160800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>166700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>197300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-7900</v>
+        <v>379000</v>
       </c>
       <c r="E89" s="3">
-        <v>296100</v>
+        <v>-7800</v>
       </c>
       <c r="F89" s="3">
-        <v>481300</v>
+        <v>294300</v>
       </c>
       <c r="G89" s="3">
-        <v>956300</v>
+        <v>478500</v>
       </c>
       <c r="H89" s="3">
-        <v>350400</v>
+        <v>950700</v>
       </c>
       <c r="I89" s="3">
-        <v>795400</v>
+        <v>348300</v>
       </c>
       <c r="J89" s="3">
+        <v>790800</v>
+      </c>
+      <c r="K89" s="3">
         <v>569100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1432200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>791900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>615000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>563900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>457800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>221800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>138000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>628700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>420200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>300600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>88200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>106500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>263300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>155300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>215800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>740900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>341600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>501400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>82400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>523700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3240000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3078000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4329000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3200000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3476000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2633000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-182900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-127700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-116400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-136900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-320200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-237200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-258000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-184600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-284000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-183700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-534700</v>
+        <v>27400</v>
       </c>
       <c r="E94" s="3">
-        <v>-507000</v>
+        <v>-531600</v>
       </c>
       <c r="F94" s="3">
-        <v>-712500</v>
+        <v>-504100</v>
       </c>
       <c r="G94" s="3">
-        <v>-449600</v>
+        <v>-708400</v>
       </c>
       <c r="H94" s="3">
-        <v>-294500</v>
+        <v>-447000</v>
       </c>
       <c r="I94" s="3">
-        <v>-400500</v>
+        <v>-292700</v>
       </c>
       <c r="J94" s="3">
+        <v>-398200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-393500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-45700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-154100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-265300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-138800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>85700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-128800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>12700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-131700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-456900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-194500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-324000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-234000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-310700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-182800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-292200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-154800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>220100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,13 +8585,14 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-471600</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -8367,41 +8601,41 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-1189400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-1182500</v>
       </c>
       <c r="I96" s="3">
-        <v>-11300</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-281500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-24300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-241200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-272200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8409,49 +8643,52 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-10100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-295800</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-446800</v>
+      </c>
+      <c r="E100" s="3">
         <v>8300</v>
       </c>
-      <c r="E100" s="3">
-        <v>804400</v>
-      </c>
       <c r="F100" s="3">
-        <v>-42800</v>
+        <v>799700</v>
       </c>
       <c r="G100" s="3">
-        <v>-1359000</v>
+        <v>-42500</v>
       </c>
       <c r="H100" s="3">
-        <v>-36400</v>
+        <v>-1351100</v>
       </c>
       <c r="I100" s="3">
-        <v>22000</v>
+        <v>-36200</v>
       </c>
       <c r="J100" s="3">
+        <v>21900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-118000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-151900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>38200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-250200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-49300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-493200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-73900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>669000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-107400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-208300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>531200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>115200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>45700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>22200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>101800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>602000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>26000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>61700</v>
+        <v>-28800</v>
       </c>
       <c r="E101" s="3">
-        <v>-72000</v>
+        <v>61300</v>
       </c>
       <c r="F101" s="3">
-        <v>-42700</v>
+        <v>-71600</v>
       </c>
       <c r="G101" s="3">
-        <v>55800</v>
+        <v>-42400</v>
       </c>
       <c r="H101" s="3">
-        <v>81500</v>
+        <v>55500</v>
       </c>
       <c r="I101" s="3">
-        <v>-43000</v>
+        <v>81100</v>
       </c>
       <c r="J101" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="K101" s="3">
         <v>69600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>76900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>23900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>13900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-19000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>32500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-33400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-22300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-95400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>58500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-8600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>21100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>44000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>31000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>9000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>30300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-472600</v>
+        <v>-69200</v>
       </c>
       <c r="E102" s="3">
-        <v>521500</v>
+        <v>-469800</v>
       </c>
       <c r="F102" s="3">
-        <v>-316700</v>
+        <v>518400</v>
       </c>
       <c r="G102" s="3">
-        <v>-796400</v>
+        <v>-314800</v>
       </c>
       <c r="H102" s="3">
-        <v>101000</v>
+        <v>-791800</v>
       </c>
       <c r="I102" s="3">
-        <v>373900</v>
+        <v>100400</v>
       </c>
       <c r="J102" s="3">
+        <v>371700</v>
+      </c>
+      <c r="K102" s="3">
         <v>127200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>317400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-161200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>388600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-127500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>483000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-260500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>213700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>326700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>188700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>519300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-96000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>119100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>36500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>10500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-156300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>4790800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>4471100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4396700</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4203800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5043400</v>
-      </c>
-      <c r="I8" s="3">
-        <v>4564100</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>4144800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4960800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6146300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4263500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4367500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3452900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3250600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3169900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1249900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2787400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2567200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3202000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3928000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4515500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4529900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4254800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4330700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>3141900</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2823600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2786700</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2868300</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3019500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2943000</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>2713700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3246800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3512800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2667000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2333100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2229300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1995300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1897500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>625800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1676100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1603700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1894400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2471300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2899500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2997100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2845600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2839000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2625700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>1648900</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1647600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1610100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1335500</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2023800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1621200</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>1431100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1714000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2633500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1596500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2034400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1223600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1255300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1272400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>624100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1111300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>963600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1307600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1456800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1616100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1532800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1409100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1491700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1442300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>929900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>969000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,71 +1358,74 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>416000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>27000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>27700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>12100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>185300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100900</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1421,11 +1441,11 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1442,109 +1462,115 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>234900</v>
-      </c>
-      <c r="E15" s="3">
-        <v>232500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>238700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>218800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>220100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>205900</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="3">
         <v>213500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>202000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>205600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>184700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>199100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>196400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>177300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>174000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>88100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>173300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>184400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>192100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>236000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>269100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>243400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>237500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>193900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>189400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>193400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>207100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>228100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>167900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>160800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>166700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>197200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>4456300</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4182800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4609000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4234200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4296800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4166100</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>4012700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4235300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4683700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3694400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3418800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3214700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2965200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2948300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>535800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2595600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2728100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2976300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3972200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4488800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4454100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4252500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4310600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3857600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>334500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>288300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-212200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-30400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>746600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>398100</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>132100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>725500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1462600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>569100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>948700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>238300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>285400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>221500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>714100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>191800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-160900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>225700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-44200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>26700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>75900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>20100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>210400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>305500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>358100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>522300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>269000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>341100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>297200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>242200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-56600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-124200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>31400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>83400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-44800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-163300</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>54100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>72400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-96300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>221000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>83700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-62000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>54000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>65600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>184400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-152000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>62700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-426500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>52700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-170700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-51800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-27200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>60900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>27100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>514400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>396600</v>
-      </c>
-      <c r="F21" s="3">
-        <v>473900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>271900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>921900</v>
-      </c>
-      <c r="I21" s="3">
-        <v>440400</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>426600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1004500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1571900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>974800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1259200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>374000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>517300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>473200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1085900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>220600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>271500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>345500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>125200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>267600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>260600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>163000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>372600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>468800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>527000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>673000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>497900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>399100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>491000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>435600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>74800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>56100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>55800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>47900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>44900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>44800</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>28600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>26200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>22100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>27000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>25400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>30300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>15100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>13300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>10400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>13400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>203100</v>
-      </c>
-      <c r="E23" s="3">
-        <v>108000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-236600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>5200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>657000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>190100</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>157600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>772400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1338300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>769700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1009300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>152400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>318800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>263600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>872200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-121600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-222900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-18500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-169300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-61300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>167200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>260400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>306600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>432500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>325100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>230100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>313900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>224900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>69500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>67700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>24100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>63900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>181500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>82500</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>142800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>140800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>281800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>183400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>207400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>46500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>93300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>77000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>84700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>29100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-46300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>55000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>17000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>23500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>72600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>48400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>81300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>72300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>49100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>87200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>100500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>133600</v>
-      </c>
-      <c r="E26" s="3">
-        <v>40200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-260700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-58800</v>
-      </c>
-      <c r="H26" s="3">
-        <v>475500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>107600</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>14800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>631600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1056500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>586400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>801900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>105900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>225500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>186600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>787500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-150600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-176600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-73500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-167400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-22100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-84700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>94500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>212000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>225300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>416800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>252900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>181000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>226700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>124400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>201600</v>
-      </c>
-      <c r="E27" s="3">
-        <v>88500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-238500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-33700</v>
-      </c>
-      <c r="H27" s="3">
-        <v>490100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>119000</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>23600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>648000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1069700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>524900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>669900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>96700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>204900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>180700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>761500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-128000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-154900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-52700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-151500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-78200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>76800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>215600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>226900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>405100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>235900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>171800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>217300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>130700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2736,24 +2797,24 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="3">
         <v>3400</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -2761,37 +2822,37 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-1800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>38300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-37700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-230600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-11200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-28600</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>56600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>124200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-31400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-83400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>44800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>163300</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-54100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-72400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>96300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-221000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-83700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>62000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-65600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-184400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>152000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-62700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>426500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-52700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>170700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>51800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>51000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>27200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>30000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>38200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>77500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>102800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>201600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>88500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-238500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-33700</v>
-      </c>
-      <c r="H33" s="3">
-        <v>490100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>119000</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>27000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>648000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1069700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>524900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>670300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>94900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>243100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>143000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>531000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-22600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-126400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-183500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-52700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-151500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-78200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>76800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>215600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>226900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>405100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>235900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>171800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>217300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>130700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>201600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>88500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-238500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-33700</v>
-      </c>
-      <c r="H35" s="3">
-        <v>490100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>119000</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>27000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>648000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1069700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>524900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>670300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>94900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>243100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>143000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>531000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-22600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-126400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-183500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-52700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-151500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-78200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>76800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>215600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>226900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>405100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>235900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>171800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>217300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>130700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,233 +3698,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1776000</v>
+        <v>1792500</v>
       </c>
       <c r="E41" s="3">
-        <v>1845300</v>
+        <v>1772300</v>
       </c>
       <c r="F41" s="3">
-        <v>2315100</v>
+        <v>1811800</v>
       </c>
       <c r="G41" s="3">
-        <v>1796600</v>
+        <v>2427700</v>
       </c>
       <c r="H41" s="3">
-        <v>2111500</v>
+        <v>1791500</v>
       </c>
       <c r="I41" s="3">
-        <v>2903300</v>
+        <v>2094600</v>
       </c>
       <c r="J41" s="3">
+        <v>2951600</v>
+      </c>
+      <c r="K41" s="3">
         <v>2802900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2445300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2324700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1935400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1767600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1895000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1411900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1489200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1826900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1772200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1558500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1231800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1359800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1273500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1224500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>690500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>676400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>700300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>581300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>925500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>991000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>443100</v>
+        <v>373000</v>
       </c>
       <c r="E42" s="3">
-        <v>594100</v>
+        <v>352800</v>
       </c>
       <c r="F42" s="3">
-        <v>427000</v>
+        <v>458700</v>
       </c>
       <c r="G42" s="3">
-        <v>359900</v>
+        <v>171200</v>
       </c>
       <c r="H42" s="3">
-        <v>364900</v>
+        <v>197000</v>
       </c>
       <c r="I42" s="3">
-        <v>376000</v>
+        <v>108000</v>
       </c>
       <c r="J42" s="3">
+        <v>257700</v>
+      </c>
+      <c r="K42" s="3">
         <v>498400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>699800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>799200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1217100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>740600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>401300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>439800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>463900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>472400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>602900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>587200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>279600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>177500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>196100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>180500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>183700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>200400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>195800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>216300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>200600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>244200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>259400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>600500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>580000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>624900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>2735900</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>2692200</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>2674800</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>2505200</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>2474300</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>2571100</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>2710400</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3865,664 +3958,685 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>2053100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1916200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2485800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2098400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2769100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2681000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2665200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2340300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2222700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2370600</v>
+        <v>2481200</v>
       </c>
       <c r="E44" s="3">
-        <v>2378400</v>
+        <v>2365500</v>
       </c>
       <c r="F44" s="3">
-        <v>2393200</v>
+        <v>2335200</v>
       </c>
       <c r="G44" s="3">
-        <v>2600000</v>
+        <v>2509700</v>
       </c>
       <c r="H44" s="3">
-        <v>2709100</v>
+        <v>2592500</v>
       </c>
       <c r="I44" s="3">
-        <v>2841500</v>
+        <v>2687500</v>
       </c>
       <c r="J44" s="3">
+        <v>2888800</v>
+      </c>
+      <c r="K44" s="3">
         <v>2824500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2969600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2790300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2308200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1783900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1547700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1346600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1420300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2019000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1953900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2064700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2275600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2303900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2609300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2626900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2830700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2987800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2446600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>89300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>506100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>640000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>161800</v>
       </c>
       <c r="I45" s="3">
+        <v>253900</v>
+      </c>
+      <c r="J45" s="3">
+        <v>124600</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>100</v>
-      </c>
-      <c r="AI45" s="3" t="s">
+      <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7287500</v>
+        <v>7504900</v>
       </c>
       <c r="E46" s="3">
-        <v>7542000</v>
+        <v>7272100</v>
       </c>
       <c r="F46" s="3">
-        <v>7524300</v>
+        <v>7786500</v>
       </c>
       <c r="G46" s="3">
-        <v>7238000</v>
+        <v>8253900</v>
       </c>
       <c r="H46" s="3">
-        <v>7777300</v>
+        <v>7217200</v>
       </c>
       <c r="I46" s="3">
-        <v>8786900</v>
+        <v>7715200</v>
       </c>
       <c r="J46" s="3">
+        <v>8933000</v>
+      </c>
+      <c r="K46" s="3">
         <v>8381600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8805000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8680700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7834500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6161000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5709900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4778100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5039700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6220500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6382300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6126600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6272800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5939600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6848100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6712900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6370100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6204900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5565400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2338900</v>
+        <v>2303200</v>
       </c>
       <c r="E47" s="3">
-        <v>2117000</v>
+        <v>2333900</v>
       </c>
       <c r="F47" s="3">
-        <v>1996300</v>
+        <v>2078600</v>
       </c>
       <c r="G47" s="3">
-        <v>2316500</v>
+        <v>2196300</v>
       </c>
       <c r="H47" s="3">
-        <v>2283000</v>
+        <v>2309800</v>
       </c>
       <c r="I47" s="3">
-        <v>2122100</v>
+        <v>2264800</v>
       </c>
       <c r="J47" s="3">
+        <v>2157400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1995700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2139000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1902400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1669800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1661200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1639100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1620400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1709100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1790700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1220500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1278300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1402500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1272900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1421300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1264500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1284800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1305300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1134900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7001100</v>
+        <v>7159600</v>
       </c>
       <c r="E48" s="3">
-        <v>7272500</v>
+        <v>6986200</v>
       </c>
       <c r="F48" s="3">
-        <v>7051200</v>
+        <v>7140500</v>
       </c>
       <c r="G48" s="3">
-        <v>6993500</v>
+        <v>7394300</v>
       </c>
       <c r="H48" s="3">
-        <v>6863500</v>
+        <v>6973400</v>
       </c>
       <c r="I48" s="3">
-        <v>6378500</v>
+        <v>6808700</v>
       </c>
       <c r="J48" s="3">
+        <v>6484500</v>
+      </c>
+      <c r="K48" s="3">
         <v>5892200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5899500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5589200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5176500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5139600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5300600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5068900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5346400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6654500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6955000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7139400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7892200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8217200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8909600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8463300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8251000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8390300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6777500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>786600</v>
+        <v>791400</v>
       </c>
       <c r="E49" s="3">
-        <v>822000</v>
+        <v>785000</v>
       </c>
       <c r="F49" s="3">
-        <v>794400</v>
+        <v>807100</v>
       </c>
       <c r="G49" s="3">
-        <v>1017800</v>
+        <v>833000</v>
       </c>
       <c r="H49" s="3">
-        <v>960600</v>
+        <v>1014900</v>
       </c>
       <c r="I49" s="3">
-        <v>925300</v>
+        <v>953000</v>
       </c>
       <c r="J49" s="3">
+        <v>940600</v>
+      </c>
+      <c r="K49" s="3">
         <v>872700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>927900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>889200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>821900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>832600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>862900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>827400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>872700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>969200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1003200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1039500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1281300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1272900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1407600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1328000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1260400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1291000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1094100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>628400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>645800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>729800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>716500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1884100</v>
+        <v>1875600</v>
       </c>
       <c r="E52" s="3">
-        <v>2289500</v>
+        <v>1880000</v>
       </c>
       <c r="F52" s="3">
-        <v>2049500</v>
+        <v>1866500</v>
       </c>
       <c r="G52" s="3">
-        <v>1736900</v>
+        <v>1380800</v>
       </c>
       <c r="H52" s="3">
-        <v>1723500</v>
+        <v>1731900</v>
       </c>
       <c r="I52" s="3">
-        <v>1666900</v>
+        <v>1709700</v>
       </c>
       <c r="J52" s="3">
+        <v>1694600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1535900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1792600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1727800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2033600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1719200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1577300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2964500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3126800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1394500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1241200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1246600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1307400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1493200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1516400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1538900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1473100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1415700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1311300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19298200</v>
+        <v>19634700</v>
       </c>
       <c r="E54" s="3">
-        <v>20043000</v>
+        <v>19257200</v>
       </c>
       <c r="F54" s="3">
-        <v>19415700</v>
+        <v>19679200</v>
       </c>
       <c r="G54" s="3">
-        <v>19302700</v>
+        <v>20360500</v>
       </c>
       <c r="H54" s="3">
-        <v>19607900</v>
+        <v>19247100</v>
       </c>
       <c r="I54" s="3">
-        <v>19879600</v>
+        <v>19451400</v>
       </c>
       <c r="J54" s="3">
+        <v>20210100</v>
+      </c>
+      <c r="K54" s="3">
         <v>18678000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19564000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18789300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17536300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15513700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15089800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15259200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16094600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17029400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16802100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16830500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18156200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18195900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>20103100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19307700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18639300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18607200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15883200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2476600</v>
+        <v>2481500</v>
       </c>
       <c r="E57" s="3">
-        <v>2495900</v>
+        <v>2471400</v>
       </c>
       <c r="F57" s="3">
-        <v>2466900</v>
+        <v>2450600</v>
       </c>
       <c r="G57" s="3">
-        <v>2337800</v>
+        <v>1842200</v>
       </c>
       <c r="H57" s="3">
-        <v>2400700</v>
+        <v>2331100</v>
       </c>
       <c r="I57" s="3">
-        <v>2417000</v>
+        <v>2381600</v>
       </c>
       <c r="J57" s="3">
+        <v>2457200</v>
+      </c>
+      <c r="K57" s="3">
         <v>2292100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2525800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2765700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2298400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1901800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1909600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1642500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1732400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1962600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1809700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1691000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2183800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2068800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2373000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2429800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2507100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2299400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2036400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1528100</v>
+        <v>1323400</v>
       </c>
       <c r="E58" s="3">
-        <v>768200</v>
+        <v>1524800</v>
       </c>
       <c r="F58" s="3">
-        <v>668700</v>
+        <v>754300</v>
       </c>
       <c r="G58" s="3">
-        <v>542000</v>
+        <v>701300</v>
       </c>
       <c r="H58" s="3">
-        <v>495700</v>
+        <v>540500</v>
       </c>
       <c r="I58" s="3">
-        <v>554700</v>
+        <v>491700</v>
       </c>
       <c r="J58" s="3">
+        <v>564000</v>
+      </c>
+      <c r="K58" s="3">
         <v>634400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1048500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>739500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>646800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>393700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>393500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>442200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>466400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>491800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>700500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>718600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>782800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>681500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>731100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>945500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1009000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1057500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>675900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>508300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>571600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>954700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>433200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>429200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>404800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>805200</v>
+        <v>899800</v>
       </c>
       <c r="E59" s="3">
-        <v>757800</v>
+        <v>803500</v>
       </c>
       <c r="F59" s="3">
-        <v>992000</v>
+        <v>755900</v>
       </c>
       <c r="G59" s="3">
-        <v>1043300</v>
+        <v>775900</v>
       </c>
       <c r="H59" s="3">
-        <v>902100</v>
+        <v>1040300</v>
       </c>
       <c r="I59" s="3">
-        <v>1010100</v>
+        <v>894900</v>
       </c>
       <c r="J59" s="3">
+        <v>1026900</v>
+      </c>
+      <c r="K59" s="3">
         <v>1099000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1102300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1017300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1146500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>663900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>488300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>379600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>400400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>554400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>370700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>376900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>483300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>535900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>492900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>426400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>529000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>684000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>603300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>509000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>526400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>410100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>337100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>411300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>458100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4809900</v>
+        <v>4704600</v>
       </c>
       <c r="E60" s="3">
-        <v>4021900</v>
+        <v>4799600</v>
       </c>
       <c r="F60" s="3">
-        <v>4127600</v>
+        <v>3960800</v>
       </c>
       <c r="G60" s="3">
-        <v>3923200</v>
+        <v>4342400</v>
       </c>
       <c r="H60" s="3">
-        <v>3798600</v>
+        <v>3911900</v>
       </c>
       <c r="I60" s="3">
-        <v>3981800</v>
+        <v>3768200</v>
       </c>
       <c r="J60" s="3">
+        <v>4048000</v>
+      </c>
+      <c r="K60" s="3">
         <v>4025600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4676600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4522500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4091700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2959400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2791300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2464300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2599200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3008800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2880900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2786600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3450000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3286200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3597000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3801800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4045200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4040900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3315500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2150400</v>
+        <v>2266300</v>
       </c>
       <c r="E61" s="3">
-        <v>2914900</v>
+        <v>2145800</v>
       </c>
       <c r="F61" s="3">
-        <v>2725100</v>
+        <v>2862000</v>
       </c>
       <c r="G61" s="3">
-        <v>2815900</v>
+        <v>2857700</v>
       </c>
       <c r="H61" s="3">
-        <v>2798300</v>
+        <v>2807800</v>
       </c>
       <c r="I61" s="3">
-        <v>2785000</v>
+        <v>2775900</v>
       </c>
       <c r="J61" s="3">
+        <v>2831300</v>
+      </c>
+      <c r="K61" s="3">
         <v>2447800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1966500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1997200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1927300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2398100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2310300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2225300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2347100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2569900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2620900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2694100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2156700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2087200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2405400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2153000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1195400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1054000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>806700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>959300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>948900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>356300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>368600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>415900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>550400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2572700</v>
+        <v>1304200</v>
       </c>
       <c r="E62" s="3">
-        <v>2597400</v>
+        <v>1225400</v>
       </c>
       <c r="F62" s="3">
-        <v>2483600</v>
+        <v>1231800</v>
       </c>
       <c r="G62" s="3">
-        <v>2430800</v>
+        <v>1165300</v>
       </c>
       <c r="H62" s="3">
-        <v>2493600</v>
+        <v>1052300</v>
       </c>
       <c r="I62" s="3">
-        <v>2358400</v>
+        <v>1113000</v>
       </c>
       <c r="J62" s="3">
+        <v>1063200</v>
+      </c>
+      <c r="K62" s="3">
         <v>2067400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2223100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2306000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2416100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2541500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2318000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3260900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3439400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3429000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3510900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3361000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3719000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3516400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3912800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3455400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3278400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3547300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2811300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10040200</v>
+        <v>9615900</v>
       </c>
       <c r="E66" s="3">
-        <v>10121600</v>
+        <v>9512700</v>
       </c>
       <c r="F66" s="3">
-        <v>9957300</v>
+        <v>9361100</v>
       </c>
       <c r="G66" s="3">
-        <v>9610600</v>
+        <v>9790500</v>
       </c>
       <c r="H66" s="3">
-        <v>9557600</v>
+        <v>9143700</v>
       </c>
       <c r="I66" s="3">
-        <v>9668500</v>
+        <v>9017800</v>
       </c>
       <c r="J66" s="3">
+        <v>9277000</v>
+      </c>
+      <c r="K66" s="3">
         <v>9043200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9430600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9365200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8947600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8220700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7761700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8228700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8679200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9335600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9322800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9168900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9726700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9348900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10441200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9925000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9051500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8925000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7391100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>5359000</v>
+        <v>5487000</v>
       </c>
       <c r="E72" s="3">
-        <v>5833300</v>
+        <v>5347600</v>
       </c>
       <c r="F72" s="3">
-        <v>5724900</v>
+        <v>5727400</v>
       </c>
       <c r="G72" s="3">
-        <v>5912800</v>
+        <v>6003500</v>
       </c>
       <c r="H72" s="3">
-        <v>5961900</v>
+        <v>5895800</v>
       </c>
       <c r="I72" s="3">
-        <v>6718600</v>
+        <v>5914400</v>
       </c>
       <c r="J72" s="3">
+        <v>6830300</v>
+      </c>
+      <c r="K72" s="3">
         <v>6616700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6613600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6265000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6022700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4972300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4877400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5029300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5304700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5389100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5010800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5033300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5159600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5837800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6405600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6299500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6466900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6443600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5915000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9258000</v>
+        <v>9413300</v>
       </c>
       <c r="E76" s="3">
-        <v>9921400</v>
+        <v>9238400</v>
       </c>
       <c r="F76" s="3">
-        <v>9458400</v>
+        <v>9741300</v>
       </c>
       <c r="G76" s="3">
-        <v>9692000</v>
+        <v>9918700</v>
       </c>
       <c r="H76" s="3">
-        <v>10050300</v>
+        <v>9664100</v>
       </c>
       <c r="I76" s="3">
-        <v>10211100</v>
+        <v>9970100</v>
       </c>
       <c r="J76" s="3">
+        <v>10380800</v>
+      </c>
+      <c r="K76" s="3">
         <v>9634900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10133300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9424100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8588600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7292900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7328000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7030500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7415500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7693800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7479300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7661600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8429500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8847000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9661900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9382700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9587900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9682200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8492100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>201600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>88500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-238500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-33700</v>
-      </c>
-      <c r="H81" s="3">
-        <v>490100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>119000</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>27000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>648000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1069700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>524900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>670300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>94900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>243100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>143000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>531000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-22600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-126400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-183500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-52700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-151500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-78200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>76800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>215600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>226900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>405100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>235900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>171800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>217300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>130700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>236500</v>
+        <v>218200</v>
       </c>
       <c r="E83" s="3">
-        <v>232500</v>
+        <v>218300</v>
       </c>
       <c r="F83" s="3">
-        <v>654700</v>
-      </c>
-      <c r="G83" s="3">
-        <v>218800</v>
+        <v>209300</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H83" s="3">
-        <v>220100</v>
+        <v>196700</v>
       </c>
       <c r="I83" s="3">
-        <v>205600</v>
+        <v>219400</v>
       </c>
       <c r="J83" s="3">
+        <v>230700</v>
+      </c>
+      <c r="K83" s="3">
         <v>240400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>206700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>205700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>184700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>226800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>197700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>178000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>186100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>415700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>211200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>400700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>222800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>337000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>269100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>243500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>237500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>193900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>189400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>193300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>207100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>228100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>168000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>160800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>166700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>197300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>379000</v>
+        <v>442100</v>
       </c>
       <c r="E89" s="3">
+        <v>392100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>327200</v>
+      </c>
+      <c r="H89" s="3">
+        <v>477100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>943200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>354100</v>
+      </c>
+      <c r="K89" s="3">
+        <v>790800</v>
+      </c>
+      <c r="L89" s="3">
+        <v>569100</v>
+      </c>
+      <c r="M89" s="3">
+        <v>1432200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="O89" s="3">
+        <v>791900</v>
+      </c>
+      <c r="P89" s="3">
         <v>-7800</v>
       </c>
-      <c r="F89" s="3">
-        <v>294300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>478500</v>
-      </c>
-      <c r="H89" s="3">
-        <v>950700</v>
-      </c>
-      <c r="I89" s="3">
-        <v>348300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>790800</v>
-      </c>
-      <c r="K89" s="3">
-        <v>569100</v>
-      </c>
-      <c r="L89" s="3">
-        <v>1432200</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-17100</v>
-      </c>
-      <c r="N89" s="3">
-        <v>791900</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>615000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-54000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>563900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>457800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>221800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>138000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>628700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>420200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>300600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>88200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>106500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>263300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>155300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>215800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>740900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>341600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>501400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>82400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>523700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3240000</v>
+        <v>-272300</v>
       </c>
       <c r="E91" s="3">
-        <v>-3078000</v>
+        <v>-304000</v>
       </c>
       <c r="F91" s="3">
-        <v>-4329000</v>
+        <v>-284200</v>
       </c>
       <c r="G91" s="3">
-        <v>-3200000</v>
+        <v>-426900</v>
       </c>
       <c r="H91" s="3">
-        <v>-3476000</v>
+        <v>-300100</v>
       </c>
       <c r="I91" s="3">
-        <v>-2633000</v>
+        <v>-324300</v>
       </c>
       <c r="J91" s="3">
+        <v>-251700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-182900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-127700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-116400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-136900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-320200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-237200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-258000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-184600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-284000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-183700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>27400</v>
+        <v>-313900</v>
       </c>
       <c r="E94" s="3">
-        <v>-531600</v>
+        <v>27300</v>
       </c>
       <c r="F94" s="3">
-        <v>-504100</v>
+        <v>-522000</v>
       </c>
       <c r="G94" s="3">
-        <v>-708400</v>
+        <v>-528600</v>
       </c>
       <c r="H94" s="3">
-        <v>-447000</v>
+        <v>-706400</v>
       </c>
       <c r="I94" s="3">
-        <v>-292700</v>
+        <v>-443400</v>
       </c>
       <c r="J94" s="3">
+        <v>-297600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-398200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-393500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-154100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-265300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-138800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>85700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-128800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>12700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-131700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-456900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-194500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-324000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-234000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-310700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-182800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-292200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-154800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>220100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,59 +8819,60 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-471600</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+        <v>470600</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
-      <c r="H96" s="3">
-        <v>-1182500</v>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+        <v>1072900</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>-11200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-281500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-24300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-241200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-272200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -8646,49 +8880,52 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-10100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-295800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-446800</v>
+        <v>-135100</v>
       </c>
       <c r="E100" s="3">
-        <v>8300</v>
+        <v>-445800</v>
       </c>
       <c r="F100" s="3">
-        <v>799700</v>
+        <v>8100</v>
       </c>
       <c r="G100" s="3">
-        <v>-42500</v>
+        <v>838600</v>
       </c>
       <c r="H100" s="3">
-        <v>-1351100</v>
+        <v>-42400</v>
       </c>
       <c r="I100" s="3">
-        <v>-36200</v>
+        <v>-1340300</v>
       </c>
       <c r="J100" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="K100" s="3">
         <v>21900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-118000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-151900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>38200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-250200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-49300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-493200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-73900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>669000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-107400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-208300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>531200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>115200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>45700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>22200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>101800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>602000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>26000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-28800</v>
+        <v>-42300</v>
       </c>
       <c r="E101" s="3">
-        <v>61300</v>
+        <v>55000</v>
       </c>
       <c r="F101" s="3">
-        <v>-71600</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-42400</v>
+        <v>82400</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H101" s="3">
-        <v>55500</v>
+        <v>67800</v>
       </c>
       <c r="I101" s="3">
-        <v>81100</v>
+        <v>82100</v>
       </c>
       <c r="J101" s="3">
+        <v>29800</v>
+      </c>
+      <c r="K101" s="3">
         <v>-42800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>69600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>76900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>23900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>13900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-19000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>32500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-28500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-33400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-22300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-95400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>58500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>21100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>44000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>31000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>9000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>30300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-69200</v>
+        <v>-1000</v>
       </c>
       <c r="E102" s="3">
-        <v>-469800</v>
+        <v>-55200</v>
       </c>
       <c r="F102" s="3">
-        <v>518400</v>
+        <v>-461000</v>
       </c>
       <c r="G102" s="3">
-        <v>-314800</v>
+        <v>562200</v>
       </c>
       <c r="H102" s="3">
-        <v>-791800</v>
+        <v>-313900</v>
       </c>
       <c r="I102" s="3">
-        <v>100400</v>
+        <v>-785500</v>
       </c>
       <c r="J102" s="3">
+        <v>102100</v>
+      </c>
+      <c r="K102" s="3">
         <v>371700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>127200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>317400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-161200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>388600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-127500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>483000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-260500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>213700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>326700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>188700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>519300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-96000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>119100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>36500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>10500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-156300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -829,86 +832,89 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>4144800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4960800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6146300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4263500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4367500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3452900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3250600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3169900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1249900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2787400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2567200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3202000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3928000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4515500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4529900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4254800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4330700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,86 +939,89 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>2713700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3246800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3512800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2667000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2333100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2229300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1995300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1897500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>625800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1676100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1603700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1894400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2471300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2899500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2997100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2845600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2839000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2625700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1037,86 +1046,89 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>1431100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1714000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2633500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1596500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2034400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1223600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1255300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1272400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>624100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1111300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>963600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1307600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1456800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1616100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1532800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1409100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1491700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1442300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>929900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>969000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,48 +1406,48 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>27000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4600</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>27700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>185300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>100900</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1444,11 +1463,11 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1465,8 +1484,11 @@
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,86 +1513,89 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3">
         <v>213500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>202000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>205600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>184700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>199100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>196400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>177300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>174000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>88100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>173300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>184400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>192100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>236000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>269100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>243400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>237500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>193900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>189400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>193400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>207100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>228100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>167900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>160800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>166700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>197200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,8 +1629,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1630,86 +1656,89 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>4012700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4235300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4683700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3694400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3418800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3214700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2965200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2948300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>535800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2595600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2728100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2976300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3972200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4488800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4454100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4252500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4310600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3857600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1734,86 +1763,89 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>132100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>725500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1462600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>569100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>948700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>238300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>285400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>221500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>714100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>191800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-160900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>225700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-44200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>75900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>20100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>210400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>305500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>358100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>522300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>269000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>341100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>297200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>242200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,86 +1909,89 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>54100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>72400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-96300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>221000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>83700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>54000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>65600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>184400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-152000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>62700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-426500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>52700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-170700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-51800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>20800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-51000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-27200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>60900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>27100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1980,86 +2016,89 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>426600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1004500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1571900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>974800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1259200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>374000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>517300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>473200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1085900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>220600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>271500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>345500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>125200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>267600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>260600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>163000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>372600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>468800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>527000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>673000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>497900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>399100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>491000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>435600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,86 +2123,89 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>28600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>28000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>26400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>27000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>30300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>15100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>13300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>13400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2188,86 +2230,89 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>157600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>772400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1338300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>769700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1009300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>152400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>318800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>263600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>872200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>13400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-121600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-222900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-18500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-169300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-61300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>167200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>260400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>306600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>432500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>325100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>230100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>313900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>224900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,86 +2337,89 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>142800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>140800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>281800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>183400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>207400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>46500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>93300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>77000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>84700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>29100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-46300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>55000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>21200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>17000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>23500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>72600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>48400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>81300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>15600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>72300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>49100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>87200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>100500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,8 +2522,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2500,86 +2551,89 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>14800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>631600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1056500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>586400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>801900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>105900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>225500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>186600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>787500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-150600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-176600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-73500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-167400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-22100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-84700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>94500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>212000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>225300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>416800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>252900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>181000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>226700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>124400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,86 +2658,89 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>23600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>648000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1069700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>524900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>669900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>96700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>204900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>180700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>761500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-128000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-154900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-52700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-151500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-78200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>76800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>215600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>226900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>405100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>235900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>171800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>217300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>130700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2812,12 +2872,12 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3">
         <v>3400</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -2825,37 +2885,37 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>38300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-37700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-230600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-11200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-28600</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,86 +3193,89 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-54100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-72400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>96300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-221000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-83700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>62000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-54000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-65600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-184400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>152000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-62700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>426500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-52700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>170700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>51800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-20800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>51000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>27200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>30000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>38200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>77500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>102800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3228,86 +3300,89 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>648000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1069700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>524900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>670300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>94900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>243100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>143000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>531000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-22600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-126400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-183500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-52700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-151500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-78200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>76800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>215600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>226900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>405100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>235900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>171800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>217300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>130700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,8 +3485,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3436,195 +3514,201 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>648000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1069700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>524900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>670300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>94900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>243100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>143000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>531000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-22600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-126400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-183500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-52700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-151500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-78200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>76800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>215600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>226900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>405100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>235900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>171800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>217300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>130700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,243 +3784,250 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1324600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1792500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1772300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1811800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2427700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1791500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2094600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2951600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2802900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2445300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2324700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1935400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1767600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1895000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1411900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1489200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1826900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1772200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1558500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1231800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1359800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1273500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1224500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>690500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>676400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>700300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>581300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>925500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>991000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>138700</v>
+      </c>
+      <c r="E42" s="3">
         <v>373000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>352800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>458700</v>
       </c>
-      <c r="G42" s="3">
-        <v>171200</v>
-      </c>
       <c r="H42" s="3">
+        <v>165300</v>
+      </c>
+      <c r="I42" s="3">
         <v>197000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>108000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>257700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>498400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>699800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>799200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1217100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>740600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>401300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>439800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>463900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>472400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>602900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>587200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>279600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>177500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>196100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>180500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>183700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>200400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>195800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>216300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>200600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>244200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>259400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>600500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>580000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>624900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2509500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2735900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2692200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2674800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2505200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2474300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2571100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2710400</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3961,189 +4053,195 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>2053100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1916200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2485800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2098400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2769100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2681000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2665200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2340300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2222700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2481100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2481200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2365500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2335200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2509700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2592500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2687500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2888800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2824500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2969600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2790300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2308200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1783900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1547700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1346600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1420300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2019000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1953900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2064700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2275600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2303900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2609300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2626900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2830700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2987800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2446600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>202700</v>
+      </c>
+      <c r="E45" s="3">
         <v>122300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>89300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>506100</v>
       </c>
-      <c r="G45" s="3">
-        <v>640000</v>
-      </c>
       <c r="H45" s="3">
+        <v>645900</v>
+      </c>
+      <c r="I45" s="3">
         <v>161800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>253900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>124600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4168,24 +4266,24 @@
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T45" s="3">
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4201,8 +4299,8 @@
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
@@ -4210,433 +4308,448 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>100</v>
       </c>
-      <c r="AJ45" s="3" t="s">
+      <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6656600</v>
+      </c>
+      <c r="E46" s="3">
         <v>7504900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7272100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7786500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8253900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7217200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7715200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8933000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8381600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8805000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8680700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7834500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6161000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5709900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4778100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5039700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6220500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6382300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6126600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6272800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5939600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6848100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6712900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6370100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6204900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5565400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2348000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2303200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2333900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2078600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2196300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2309800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2264800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2157400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1995700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2139000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1902400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1669800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1661200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1639100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1620400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1709100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1790700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1220500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1278300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1402500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1272900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1421300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1264500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1284800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1305300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1134900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6860100</v>
+      </c>
+      <c r="E48" s="3">
         <v>7159600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6986200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7140500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7394300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6973400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6808700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6484500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5892200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5899500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5589200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5176500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5139600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5300600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5068900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5346400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6654500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6955000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7139400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7892200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8217200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8909600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8463300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8251000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8390300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6777500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>742500</v>
+      </c>
+      <c r="E49" s="3">
         <v>791400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>785000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>807100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>833000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1014900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>953000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>940600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>872700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>927900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>889200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>821900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>832600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>862900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>827400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>872700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>969200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1003200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1039500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1281300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1272900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1407600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1328000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1260400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1291000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1094100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>628400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>645800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>729800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>716500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1272400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1875600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1880000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1866500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1380800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1731900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1709700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1694600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1535900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1792600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1727800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2033600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1719200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1577300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2964500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3126800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1394500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1241200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1246600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1307400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1493200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1516400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1538900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1473100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1415700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1311300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18253100</v>
+      </c>
+      <c r="E54" s="3">
         <v>19634700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19257200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19679200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20360500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19247100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19451400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20210100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18678000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19564000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18789300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17536300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15513700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15089800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15259200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16094600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17029400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16802100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16830500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18156200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18195900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>20103100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19307700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18639300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18607200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15883200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1733100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2481500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2471400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2450600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1842200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2331100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2381600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2457200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2292100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2525800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2765700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2298400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1901800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1909600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1642500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1732400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1962600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1809700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1691000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2183800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2068800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2373000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2429800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2507100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2299400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2036400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1021100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1323400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1524800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>754300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>701300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>540500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>491700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>564000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>634400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1048500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>739500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>646800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>393700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>393500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>442200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>466400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>491800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>700500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>718600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>782800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>681500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>731100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>945500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1009000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1057500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>675900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>508300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>571600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>954700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>433200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>429200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>404800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>701400</v>
+      </c>
+      <c r="E59" s="3">
         <v>899800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>803500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>755900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>775900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1040300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>894900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1026900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1099000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1102300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1017300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1146500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>663900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>488300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>379600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>554400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>370700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>376900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>483300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>535900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>492900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>426400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>529000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>684000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>603300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>509000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>526400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>410100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>337100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>411300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>458100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4349200</v>
+      </c>
+      <c r="E60" s="3">
         <v>4704600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4799600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3960800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4342400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3911900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3768200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4048000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4025600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4676600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4522500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4091700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2959400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2791300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2464300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2599200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3008800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2880900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2786600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3450000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3286200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3597000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3801800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4045200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4040900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3315500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2037400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2266300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2145800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2862000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2857700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2807800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2775900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2831300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2447800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1966500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1997200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1927300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2398100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2310300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2225300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2347100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2569900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2620900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2694100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2156700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2087200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2405400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2153000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1195400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1054000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>806700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>959300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>948900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>356300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>368600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>415900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>550400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1127800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1304200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1225400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1231800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1165300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1052300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1113000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1063200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2067400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2223100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2306000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2416100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2541500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2318000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3260900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3439400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3429000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3510900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3361000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3719000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3516400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3912800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3455400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3278400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3547300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2811300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8795000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9615900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9512700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9361100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9790500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9143700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9017800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9277000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9043200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9430600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9365200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8947600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8220700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7761700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8228700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8679200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9335600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9322800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9168900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9726700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9348900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10441200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9925000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9051500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8925000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7391100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5259200</v>
+      </c>
+      <c r="E72" s="3">
         <v>5487000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5347600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5727400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6003500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5895800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5914400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6830300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6616700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6613600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6265000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6022700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4972300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4877400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5029300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5304700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5389100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5010800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5033300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5159600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5837800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6405600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6299500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6466900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6443600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5915000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8930700</v>
+      </c>
+      <c r="E76" s="3">
         <v>9413300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9238400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9741300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9918700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9664100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9970100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10380800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9634900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10133300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9424100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8588600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7292900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7328000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7030500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7415500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7693800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7479300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7661600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8429500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8847000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9661900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9382700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9587900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9682200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8492100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,117 +7537,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7484,86 +7678,89 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>648000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1069700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>524900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>670300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>94900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>243100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>143000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>531000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-22600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-126400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-183500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-52700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-151500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-78200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>76800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>215600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>226900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>405100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>235900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>171800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>217300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>130700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E83" s="3">
         <v>218200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>218300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>209300</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>196700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>219400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>230700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>240400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>206700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>205700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>184700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>226800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>197700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>178000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>186100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>415700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>211200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>400700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>222800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>337000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>269100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>243500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>237500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>193900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>189400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>193300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>207100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>228100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>168000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>160800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>166700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>197300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>581200</v>
+      </c>
+      <c r="E89" s="3">
         <v>442100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>392100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>327200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>477100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>943200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>354100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>790800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>569100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1432200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>791900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>615000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-54000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>563900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>457800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>221800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>138000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>628700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>420200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>300600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>88200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>106500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>263300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>155300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>215800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>740900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>341600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>501400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>82400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>523700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-384700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-272300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-304000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-284200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-426900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-324300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-251700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-182900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-127700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-116400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-136900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-320200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-237200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-258000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-184600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-284000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-183700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-313900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>27300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-522000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-528600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-706400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-443400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-297600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-398200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-393500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-45700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-154100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-265300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-138800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>85700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-128800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>12700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-131700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-456900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-194500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-324000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-234000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-310700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-182800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-292200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-154800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>220100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,62 +9052,63 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>470600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>1072900</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>-11200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-281500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-24300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-241200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-272200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -8883,49 +9116,52 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-10100</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-295800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-569600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-135100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-445800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>838600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-42400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1340300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-118000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-151900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>38200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-250200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-49300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-493200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-73900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>669000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-107400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-208300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>531200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>115200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>45700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>22200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>101800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>602000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>26000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-42300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>55000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>82400</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>67800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>82100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>29800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-42800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>69600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>76900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>23900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>13900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>32500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-28500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-33400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-22300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-95400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>58500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-8600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>21100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>44000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>31000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>9000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-336800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-55200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-461000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>562200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-313900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-785500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>102100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>371700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>127200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>317400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-161200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>388600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-127500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>483000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-260500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>213700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>326700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>188700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>519300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-96000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>119100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>36500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-156300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,86 +839,89 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>4144800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4960800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6146300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4263500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4367500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3452900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3250600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3169900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1249900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2787400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2567200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3202000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3928000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4515500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4529900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4254800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4330700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -942,86 +949,89 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>2713700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3246800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3512800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2667000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2333100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2229300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1995300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1897500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>625800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1676100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1603700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1894400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2471300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2899500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2997100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2845600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2839000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2625700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1049,86 +1059,89 @@
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>1431100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1714000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2633500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1596500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2034400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1223600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1255300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1272400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>624100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1111300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>963600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1307600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1456800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1616100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1532800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1409100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1491700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1442300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>929900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>969000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,48 +1429,48 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>27000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4600</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>27700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>185300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100900</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1466,11 +1486,11 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1487,8 +1507,11 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,86 +1539,89 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="3">
         <v>213500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>202000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>205600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>184700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>199100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>196400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>177300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>174000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>88100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>173300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>184400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>192100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>236000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>269100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>243400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>237500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>193900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>189400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>193400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>207100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>228100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>167900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>160800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>166700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>197200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,8 +1656,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1659,86 +1686,89 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>4012700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4235300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4683700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3694400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3418800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3214700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2965200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2948300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>535800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2595600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2728100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2976300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3972200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4488800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4454100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4252500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4310600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3857600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1766,86 +1796,89 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>132100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>725500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1462600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>569100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>948700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>238300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>285400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>221500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>714100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>191800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-160900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>225700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-44200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>26700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>75900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>20100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>210400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>305500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>358100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>522300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>269000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>341100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>297200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>242200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,86 +1946,89 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>54100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>72400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-96300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>221000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>83700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-62000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>54000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>65600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>184400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-152000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>62700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-426500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>52700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-170700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-51800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>20800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-51000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-27200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>60900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>27100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2019,86 +2056,89 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>426600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1004500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1571900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>974800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1259200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>374000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>517300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>473200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1085900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>220600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>271500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>345500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>125200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>267600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>260600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>163000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>372600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>468800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>527000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>673000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>497900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>399100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>491000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>435600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,86 +2166,89 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>28600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>28000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>26200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>26400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>22100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>27000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>30300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>15100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>13300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>13400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2233,86 +2276,89 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>157600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>772400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1338300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>769700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1009300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>152400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>318800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>263600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>872200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-121600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-222900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-18500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-169300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-61300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>167200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>260400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>306600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>432500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>325100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>230100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>313900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>224900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2340,86 +2386,89 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>142800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>140800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>281800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>183400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>207400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>46500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>93300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>77000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>84700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>24500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>29100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-46300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>55000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>21200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>17000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>23500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>72600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>48400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>81300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>15600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>72300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>49100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>87200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>100500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,8 +2574,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2554,86 +2606,89 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>14800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>631600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1056500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>586400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>801900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>105900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>225500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>186600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>787500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-150600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-176600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-73500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-167400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-22100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-84700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>94500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>212000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>225300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>416800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>252900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>181000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>226700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>124400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2661,86 +2716,89 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>23600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>648000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1069700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>524900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>669900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>96700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>204900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>180700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>761500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-128000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-154900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-52700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-151500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-78200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>76800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>215600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>226900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>405100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>235900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>171800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>217300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>130700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2875,12 +2936,12 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="3">
         <v>3400</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -2888,37 +2949,37 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-1800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>38300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-37700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-230600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-11200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-28600</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,86 +3266,89 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-54100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-72400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>96300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-221000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-83700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>62000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-54000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-65600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-184400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>152000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-62700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>426500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-52700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>170700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>51800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-20800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>51000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>27200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>30000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>38200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>77500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>102800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3303,86 +3376,89 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>27000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>648000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1069700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>524900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>670300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>94900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>243100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>143000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>531000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-22600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-126400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-183500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-52700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-151500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-78200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>76800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>215600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>226900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>405100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>235900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>171800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>217300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>130700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,8 +3564,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3517,198 +3596,204 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>27000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>648000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1069700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>524900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>670300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>94900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>243100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>143000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>531000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-22600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-126400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-183500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-52700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-151500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-78200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>76800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>215600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>226900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>405100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>235900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>171800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>217300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>130700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,252 +3871,259 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1800900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1324600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1792500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1772300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1811800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2427700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1791500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2094600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2951600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2802900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2445300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2324700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1935400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1767600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1895000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1411900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1489200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1826900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1772200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1558500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1231800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1359800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1273500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1224500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>690500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>676400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>700300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>581300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>925500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>991000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>279800</v>
+      </c>
+      <c r="E42" s="3">
         <v>138700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>373000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>352800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>458700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>165300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>197000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>108000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>257700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>498400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>699800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>799200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1217100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>740600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>401300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>439800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>463900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>472400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>602900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>587200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>279600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>177500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>196100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>180500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>183700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>200400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>195800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>216300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>200600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>244200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>259400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>600500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>580000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>624900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2960500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2509500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2735900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2692200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2674800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2505200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2474300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2571100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2710400</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4056,195 +4149,201 @@
         <v>0</v>
       </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>2053100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1916200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2485800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2098400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2769100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2681000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2665200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2340300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2222700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2595900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2481100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2481200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2365500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2335200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2509700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2592500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2687500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2888800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2824500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2969600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2790300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2308200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1783900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1547700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1346600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1420300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2019000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1953900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2064700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2275600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2303900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2609300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2626900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2830700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2987800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2446600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E45" s="3">
         <v>202700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>122300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>89300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>506100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>645900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>161800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>253900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>124600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4269,24 +4368,24 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4302,8 +4401,8 @@
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG45" s="3">
         <v>0</v>
@@ -4311,445 +4410,460 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ45" s="3">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK45" s="3">
         <v>100</v>
       </c>
-      <c r="AK45" s="3" t="s">
+      <c r="AL45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7759500</v>
+      </c>
+      <c r="E46" s="3">
         <v>6656600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7504900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7272100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7786500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8253900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7217200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7715200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8933000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8381600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8805000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8680700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7834500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6161000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5709900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4778100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5039700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6220500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6382300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6126600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6272800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5939600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6848100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6712900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6370100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6204900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5565400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2252000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2348000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2303200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2333900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2078600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2196300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2309800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2264800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2157400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1995700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2139000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1902400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1669800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1661200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1639100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1620400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1709100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1790700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1220500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1278300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1402500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1272900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1421300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1264500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1284800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1305300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1134900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7156500</v>
+      </c>
+      <c r="E48" s="3">
         <v>6860100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7159600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6986200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7140500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7394300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6973400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6808700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6484500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5892200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5899500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5589200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5176500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5139600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5300600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5068900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5346400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6654500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6955000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7139400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7892200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8217200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8909600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8463300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8251000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8390300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6777500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>753800</v>
+      </c>
+      <c r="E49" s="3">
         <v>742500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>791400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>785000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>807100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>833000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1014900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>953000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>940600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>872700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>927900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>889200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>821900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>832600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>862900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>827400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>872700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>969200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1003200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1039500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1281300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1272900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1407600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1328000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1260400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1291000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1094100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>628400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>645800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>729800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>716500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1855000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1272400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1875600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1880000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1866500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1380800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1731900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1709700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1694600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1535900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1792600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1727800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2033600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1719200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1577300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2964500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3126800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1394500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1241200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1246600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1307400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1493200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1516400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1538900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1473100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1415700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1311300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19776800</v>
+      </c>
+      <c r="E54" s="3">
         <v>18253100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19634700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19257200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19679200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20360500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19247100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19451400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20210100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18678000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19564000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18789300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17536300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15513700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15089800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15259200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16094600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17029400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16802100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16830500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18156200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18195900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20103100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19307700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18639300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18607200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15883200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2560900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1733100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2481500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2471400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2450600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1842200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2331100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2381600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2457200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2292100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2525800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2765700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2298400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1901800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1909600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1642500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1732400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1962600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1809700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1691000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2183800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2068800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2373000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2429800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2507100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2299400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2036400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1021100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1323400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1524800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>754300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>701300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>540500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>491700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>564000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>634400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1048500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>739500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>646800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>393700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>393500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>442200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>466400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>491800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>700500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>718600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>782800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>681500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>731100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>945500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1009000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1057500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>675900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>508300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>571600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>954700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>433200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>429200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>404800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>892200</v>
+      </c>
+      <c r="E59" s="3">
         <v>701400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>899800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>803500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>755900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>775900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1040300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>894900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1026900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1099000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1102300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1017300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1146500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>663900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>488300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>379600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>554400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>370700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>376900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>483300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>535900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>492900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>426400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>529000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>684000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>603300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>509000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>526400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>410100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>337100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>411300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>458100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4703100</v>
+      </c>
+      <c r="E60" s="3">
         <v>4349200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4704600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4799600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3960800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4342400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3911900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3768200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4048000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4025600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4676600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4522500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4091700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2959400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2791300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2464300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2599200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3008800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2880900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2786600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3450000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3286200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3597000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3801800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4045200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4040900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3315500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2283400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2037400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2266300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2145800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2862000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2857700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2807800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2775900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2831300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2447800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1966500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1997200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1927300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2398100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2310300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2225300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2347100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2569900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2620900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2694100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2156700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2087200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2405400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2153000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1195400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1054000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>806700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>959300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>948900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>356300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>368600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>415900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>550400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1088100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1127800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1304200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1225400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1231800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1165300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1052300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1113000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1063200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2067400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2223100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2306000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2416100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2541500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2318000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3260900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3439400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3429000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3510900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3361000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3719000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3516400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3912800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3455400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3278400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3547300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2811300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9394400</v>
+      </c>
+      <c r="E66" s="3">
         <v>8795000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9615900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9512700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9361100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9790500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9143700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9017800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9277000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9043200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9430600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9365200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8947600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8220700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7761700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8228700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8679200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9335600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9322800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9168900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9726700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9348900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10441200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9925000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9051500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8925000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7391100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6126400</v>
+      </c>
+      <c r="E72" s="3">
         <v>5259200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5487000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5347600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5727400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6003500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5895800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5914400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6830300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6616700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6613600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6265000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6022700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4972300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4877400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5029300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5304700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5389100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5010800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5033300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5159600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5837800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6405600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6299500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6466900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6443600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5915000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9735200</v>
+      </c>
+      <c r="E76" s="3">
         <v>8930700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9413300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9238400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9741300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9918700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9664100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9970100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10380800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9634900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10133300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9424100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8588600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7292900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7328000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7030500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7415500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7693800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7479300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7661600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8429500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8847000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9661900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9382700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9587900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9682200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8492100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,120 +7729,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7681,86 +7876,89 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>27000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>648000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1069700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>524900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>670300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>94900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>243100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>143000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>531000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-22600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-126400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-183500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-52700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-151500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-78200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>76800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>215600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>226900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>405100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>235900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>171800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>217300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>130700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>228200</v>
+      </c>
+      <c r="E83" s="3">
         <v>199600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>218200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>218300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>209300</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>196700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>219400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>230700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>240400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>206700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>205700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>184700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>226800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>197700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>178000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>186100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>415700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>211200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>400700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>222800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>337000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>269100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>243500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>237500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>193900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>189400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>193300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>207100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>228100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>168000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>160800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>166700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>197300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>378300</v>
+      </c>
+      <c r="E89" s="3">
         <v>581200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>442100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>392100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>327200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>477100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>943200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>354100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>790800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>569100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1432200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>791900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>615000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-54000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>563900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>457800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>221800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>138000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>628700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>420200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>300600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>88200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>106500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>263300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>155300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>215800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>740900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>341600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>501400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>82400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>523700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-257000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-384700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-272300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-304000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-284200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-426900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-324300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-251700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-182900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-127700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-116400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-136900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-320200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-237200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-258000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-184600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-284000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-183700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-260600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-374000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-313900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>27300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-522000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-528600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-706400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-443400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-297600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-398200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-393500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-45700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-154100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-265300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-138800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>85700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-128800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>12700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-131700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-456900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-194500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-324000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-234000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-310700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-182800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-292200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-154800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>220100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,65 +9286,66 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>470600</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>1072900</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>-11200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-281500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-241200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-272200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -9119,49 +9353,52 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-295800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>343600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-569600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-135100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-445800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>838600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-42400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1340300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-118000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-151900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>38200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-250200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-49300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-493200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-73900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>669000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-107400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-208300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>531200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>115200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>45700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>22200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>101800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>602000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-75000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-42300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>55000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>82400</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>67800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>82100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>29800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-42800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>69600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>76900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>23900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-19000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>32500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-28500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-33400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-22300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-95400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>58500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>21100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>44000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>31000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>30300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>370300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-336800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-55200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-461000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>562200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-313900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-785500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>102100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>371700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>127200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>317400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-161200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>388600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-127500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>483000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-260500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>213700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>326700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>188700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>519300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-96000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>119100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>36500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>10500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-156300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -842,86 +846,89 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>4144800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4960800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6146300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4263500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4367500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3452900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3250600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3169900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1249900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2787400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2567200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3202000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3928000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4515500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4529900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4254800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4330700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -952,86 +959,89 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>2713700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3246800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3512800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2667000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2333100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2229300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1995300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1897500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>625800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1676100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1603700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1894400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2471300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2899500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2997100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2845600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2839000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2625700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1062,86 +1072,89 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>1431100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1714000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2633500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1596500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2034400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1223600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1255300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1272400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>624100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1111300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>963600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1307600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1456800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1616100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1532800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1409100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1491700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1442300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>929900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>969000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,48 +1452,48 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>27000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4600</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>27700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>185300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>100900</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1489,11 +1509,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1542,86 +1565,89 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="3">
         <v>213500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>202000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>205600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>184700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>199100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>196400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>177300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>174000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>88100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>173300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>184400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>192100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>236000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>269100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>243400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>237500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>193900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>189400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>193400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>207100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>228100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>167900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>160800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>166700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>197200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,8 +1683,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1689,86 +1716,89 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>4012700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4235300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4683700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3694400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3418800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3214700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2965200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2948300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>535800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2595600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2728100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2976300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3972200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4488800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4454100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4252500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4310600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3857600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1799,86 +1829,89 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>132100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>725500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1462600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>569100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>948700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>238300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>285400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>221500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>714100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>191800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-160900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>225700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-44200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>75900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>210400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>305500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>358100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>522300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>269000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>341100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>297200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>242200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,86 +1983,89 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>54100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>72400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-96300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>221000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>83700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-62000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>54000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>65600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>184400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-152000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>62700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-426500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>52700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-170700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-51800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>20800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-51000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-27200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>60900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>27100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2059,86 +2096,89 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>426600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1004500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1571900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>974800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1259200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>374000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>517300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>473200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1085900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>220600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>271500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>345500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>125200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>267600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>260600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>163000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>372600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>468800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>527000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>673000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>497900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>399100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>491000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>435600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,86 +2209,89 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>28600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>28000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>26200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>26400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>22100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>27000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>25000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>30300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>15100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>13300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>12400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>10400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>13400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2279,86 +2322,89 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>157600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>772400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1338300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>769700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1009300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>152400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>318800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>263600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>872200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-121600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-222900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-18500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-169300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-61300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>167200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>260400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>306600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>432500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>325100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>230100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>313900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>224900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,86 +2435,89 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>142800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>140800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>281800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>183400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>207400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>46500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>93300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>77000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>84700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>24500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>29100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-46300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>55000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>17000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>23500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>72600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>48400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>81300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>15600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>72300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>49100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>87200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>100500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,8 +2626,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2609,86 +2661,89 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>14800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>631600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1056500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>586400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>801900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>105900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>225500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>186600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>787500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-150600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-176600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-73500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-167400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-84700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>94500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>212000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>225300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>416800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>252900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>181000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>226700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>124400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2719,86 +2774,89 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>23600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>648000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1069700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>524900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>669900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>96700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>204900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>180700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>761500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-128000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-154900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-52700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-151500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-78200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>76800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>215600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>226900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>405100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>235900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>171800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>217300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>130700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2939,12 +3000,12 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3">
         <v>3400</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
@@ -2952,37 +3013,37 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1800</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>38300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-37700</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-230600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-11200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>1600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,86 +3339,89 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-54100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-72400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>96300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-221000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-83700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>62000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-54000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-65600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-184400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>152000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-62700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>426500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-52700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>170700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>51800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-20800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>51000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>27200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>30000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>38200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>77500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>102800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3379,86 +3452,89 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>27000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>648000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1069700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>524900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>670300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>94900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>243100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>143000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>531000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-22600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-126400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-183500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-52700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-151500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-78200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>76800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>215600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>226900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>405100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>235900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>171800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>217300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>130700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,8 +3643,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3599,201 +3678,207 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>27000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>648000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1069700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>524900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>670300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>94900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>243100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>143000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>531000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-22600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-126400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-183500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-52700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-151500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-78200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>76800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>215600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>226900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>405100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>235900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>171800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>217300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>130700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,261 +3958,268 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1859300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1800900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1324600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1792500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1772300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1811800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2427700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1791500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2094600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2951600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2802900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2445300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2324700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1935400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1767600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1895000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1411900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1489200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1826900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1772200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1558500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1231800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1359800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1224500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>690500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>676400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>700300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>581300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>925500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>991000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>301600</v>
+      </c>
+      <c r="E42" s="3">
         <v>279800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>138700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>373000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>352800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>458700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>165300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>197000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>108000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>257700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>498400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>699800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>799200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1217100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>740600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>401300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>439800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>463900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>472400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>602900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>587200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>279600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>177500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>196100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>180500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>183700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>200400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>195800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>216300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>200600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>244200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>259400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>600500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>580000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>624900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2788000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2960500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2509500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2735900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2692200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2674800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2505200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2474300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2571100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2710400</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4152,201 +4245,207 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>2053100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1916200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2485800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2098400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2769100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2681000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2665200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2340300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2222700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2626600</v>
+      </c>
+      <c r="E44" s="3">
         <v>2595900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2481100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2481200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2365500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2335200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2509700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2592500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2687500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2888800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2824500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2969600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2790300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2308200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1783900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1547700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1346600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1420300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2019000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1953900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2064700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2275600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2303900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2609300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2626900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2830700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2987800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2446600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E45" s="3">
         <v>122500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>202700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>122300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>89300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>506100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>645900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>161800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>253900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>124600</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4371,24 +4470,24 @@
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4404,8 +4503,8 @@
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG45" s="3">
-        <v>0</v>
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH45" s="3">
         <v>0</v>
@@ -4413,457 +4512,472 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK45" s="3">
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL45" s="3">
         <v>100</v>
       </c>
-      <c r="AL45" s="3" t="s">
+      <c r="AM45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7722400</v>
+      </c>
+      <c r="E46" s="3">
         <v>7759500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6656600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7504900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7272100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7786500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8253900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7217200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7715200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8933000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8381600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8805000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8680700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7834500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6161000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5709900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4778100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5039700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6220500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6382300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6126600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6272800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5939600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6848100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6712900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6370100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6204900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5565400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2269100</v>
+      </c>
+      <c r="E47" s="3">
         <v>2252000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2348000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2303200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2333900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2078600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2196300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2309800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2264800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2157400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1995700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2139000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1902400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1669800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1661200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1639100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1620400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1709100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1790700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1220500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1278300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1402500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1272900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1421300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1264500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1284800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1305300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1134900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7516500</v>
+      </c>
+      <c r="E48" s="3">
         <v>7156500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6860100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7159600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6986200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7140500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7394300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6973400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6808700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6484500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5892200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5899500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5589200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5176500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5139600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5300600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5068900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5346400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6654500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6955000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7139400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7892200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8217200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8909600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8463300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8251000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8390300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6777500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>780100</v>
+      </c>
+      <c r="E49" s="3">
         <v>753800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>742500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>791400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>785000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>807100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>833000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1014900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>953000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>940600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>872700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>927900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>889200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>821900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>832600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>862900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>827400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>872700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>969200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1003200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1039500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1281300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1272900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1407600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1328000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1260400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1291000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1094100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>628400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>645800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>729800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>716500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1807500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1855000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1272400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1875600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1880000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1866500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1380800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1731900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1709700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1694600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1535900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1792600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1727800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2033600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1719200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1577300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2964500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3126800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1394500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1241200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1246600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1307400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1493200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1516400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1538900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1473100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1415700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1311300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20095600</v>
+      </c>
+      <c r="E54" s="3">
         <v>19776800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18253100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19634700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19257200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19679200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20360500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19247100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19451400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20210100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18678000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19564000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18789300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17536300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15513700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15089800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15259200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16094600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17029400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16802100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16830500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18156200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18195900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>20103100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19307700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18639300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18607200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15883200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2523000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2560900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1733100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2481500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2471400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2450600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1842200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2331100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2381600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2457200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2292100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2525800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2765700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2298400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1901800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1909600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1642500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1732400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1962600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1809700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1691000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2183800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2068800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2373000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2429800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2507100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2299400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2036400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>762100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1250000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1021100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1323400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1524800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>754300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>701300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>540500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>491700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>564000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>634400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1048500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>739500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>646800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>393700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>393500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>442200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>466400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>491800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>700500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>718600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>782800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>681500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>731100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>945500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1009000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1057500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>675900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>508300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>571600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>954700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>433200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>429200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>404800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>734600</v>
+      </c>
+      <c r="E59" s="3">
         <v>892200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>701400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>899800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>803500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>755900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>775900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1040300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>894900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1026900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1099000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1102300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1017300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1146500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>663900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>488300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>379600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>400400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>554400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>370700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>376900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>483300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>535900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>492900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>426400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>529000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>684000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>603300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>509000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>526400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>410100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>337100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>411300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>458100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4019700</v>
+      </c>
+      <c r="E60" s="3">
         <v>4703100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4349200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4704600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4799600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3960800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4342400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3911900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3768200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4048000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4025600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4676600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4522500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4091700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2959400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2791300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2464300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2599200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3008800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2880900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2786600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3450000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3286200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3597000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3801800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4045200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4040900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3315500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2949500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2283400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2037400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2266300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2145800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2862000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2857700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2807800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2775900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2831300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2447800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1966500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1997200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1927300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2398100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2310300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2225300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2347100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2569900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2620900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2694100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2156700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2087200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2405400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2153000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1195400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1054000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>806700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>959300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>948900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>356300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>368600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>415900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>550400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1142000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1088100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1127800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1304200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1225400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1231800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1165300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1052300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1113000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1063200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2067400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2223100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2306000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2416100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2541500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2318000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3260900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3439400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3429000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3510900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3361000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3719000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3516400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3912800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3455400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3278400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3547300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2811300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9558300</v>
+      </c>
+      <c r="E66" s="3">
         <v>9394400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8795000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9615900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9512700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9361100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9790500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9143700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9017800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9277000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9043200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9430600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9365200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8947600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8220700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7761700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8228700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8679200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9335600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9322800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9168900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9726700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9348900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10441200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9925000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9051500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8925000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7391100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5939300</v>
+      </c>
+      <c r="E72" s="3">
         <v>6126400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5259200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5487000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5347600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5727400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6003500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5895800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5914400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6830300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6616700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6613600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6265000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6022700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4972300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4877400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5029300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5304700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5389100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5010800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5033300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5159600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5837800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6405600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6299500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6466900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6443600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5915000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9811900</v>
+      </c>
+      <c r="E76" s="3">
         <v>9735200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8930700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9413300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9238400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9741300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9918700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9664100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9970100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10380800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9634900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10133300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9424100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8588600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7292900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7328000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7030500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7415500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7693800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7479300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7661600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8429500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8847000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9661900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9382700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9587900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9682200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8492100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,123 +7921,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7879,86 +8074,89 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>27000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>648000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1069700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>524900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>670300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>94900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>243100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>143000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>531000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-22600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-126400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-183500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-52700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-151500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-78200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>76800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>215600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>226900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>405100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>235900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>171800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>217300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>130700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>234400</v>
+      </c>
+      <c r="E83" s="3">
         <v>228200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>199600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>218200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>218300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>209300</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>196700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>219400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>230700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>240400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>206700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>205700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>184700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>226800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>197700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>178000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>186100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>415700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>211200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>400700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>222800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>337000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>269100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>243500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>237500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>193900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>189400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>193300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>207100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>228100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>168000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>160800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>166700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>197300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>755200</v>
+      </c>
+      <c r="E89" s="3">
         <v>378300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>581200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>442100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>392100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>327200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>477100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>943200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>354100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>790800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>569100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1432200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>791900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>615000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-54000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>563900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>457800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>221800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>138000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>628700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>420200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>300600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>88200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>106500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>263300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>155300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>215800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>740900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>341600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>501400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>82400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>523700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-262700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-257000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-384700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-272300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-304000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-284200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-426900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-324300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-251700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-182900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-127700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-116400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-136900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-320200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-237200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-258000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-184600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-284000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-183700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-268700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-260600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-374000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-313900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>27300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-522000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-528600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-706400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-443400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-297600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-398200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-393500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-45700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-154100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-265300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-138800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>85700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-128800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>12700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-131700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-456900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-194500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-324000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-234000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-310700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-182800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-292200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-154800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>220100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,68 +9520,69 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="D96" s="3">
+        <v>439400</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>470600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>1072900</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>-11200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-281500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-24300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-241200</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-272200</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -9356,49 +9590,52 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-295800</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-528300</v>
+      </c>
+      <c r="E100" s="3">
         <v>343600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-569600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-135100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-445800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>838600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-42400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1340300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-36800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>21900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-118000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-151900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>38200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-250200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-49300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-493200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-73900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>669000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-107400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-208300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>531200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>115200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>45700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>22200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>101800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>602000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>26000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E101" s="3">
         <v>60200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-75000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-42300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>55000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>82400</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>67800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>82100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>29800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-42800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>69600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>76900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>23900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>13900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-19000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>32500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-28500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-33400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-22300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-95400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>58500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>21100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>44000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>31000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>9000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>30300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E102" s="3">
         <v>370300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-336800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-55200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-461000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>562200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-313900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-785500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>102100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>371700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>127200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>317400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-161200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>388600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-127500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>483000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-260500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>213700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>326700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>188700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>519300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-96000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>119100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>36500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>10500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-156300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,170 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -856,86 +859,89 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>4144800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4960800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6146300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4263500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4367500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3452900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3250600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3169900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1249900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2787400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2567200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3202000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3928000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4515500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4529900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4254800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4330700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,86 +978,89 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>2713700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3246800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3512800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2667000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2333100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2229300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1995300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1897500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>625800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1676100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1603700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1894400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2471300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2899500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2997100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2845600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2839000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2625700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1088,86 +1097,89 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>1431100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1714000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2633500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1596500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2034400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1223600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1255300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1272400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>624100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1111300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>963600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1307600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1456800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1616100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1532800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1409100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1491700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1442300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>929900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>969000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1478,48 +1497,48 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>27000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>27700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>6500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>7600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>185300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>100900</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1535,11 +1554,11 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
@@ -1556,8 +1575,11 @@
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,86 +1616,89 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3">
         <v>213500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>202000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>205600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>184700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>199100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>196400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>177300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>174000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>88100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>173300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>184400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>192100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>236000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>269100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>243400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>237500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>193900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>189400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>193400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>207100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>228100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>167900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>160800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>166700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>197200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,8 +1736,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1749,86 +1775,89 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>4012700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4235300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4683700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3694400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3418800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3214700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2965200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2948300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>535800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2595600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2728100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2976300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3972200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4488800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4454100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4252500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4310600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3857600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1865,86 +1894,89 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>132100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>725500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1462600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>569100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>948700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>238300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>285400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>221500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>714100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>191800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-160900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>225700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>26700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>75900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>20100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>210400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>305500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>358100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>522300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>269000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>341100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>297200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>242200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2017,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,86 +2056,89 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>54100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>72400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-96300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>221000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>83700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-62000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>54000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>65600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>184400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-152000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>62700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-426500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>52700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-170700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-51800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>20800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-51000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-27200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>60900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>27100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2139,86 +2175,89 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>426600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1004500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1571900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>974800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1259200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>374000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>517300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>473200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1085900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>220600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>271500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>345500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>125200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>267600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>260600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>163000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>372600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>468800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>527000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>673000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>497900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>399100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>491000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>435600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2255,86 +2294,89 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>28600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>25400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>28000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>26200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>26400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>22100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>27000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>20200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>30300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>16100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>15100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>13300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>4700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>10400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>13400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2371,86 +2413,89 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>157600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>772400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1338300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>769700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1009300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>152400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>318800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>263600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>872200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>13400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-121600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-222900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-169300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-61300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>167200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>260400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>306600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>432500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>325100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>230100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>313900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>224900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2487,86 +2532,89 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
         <v>142800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>140800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>281800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>183400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>207400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>46500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>93300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>77000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>84700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>24500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>29100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-46300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>55000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>17000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>23500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>72600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>48400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>81300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>15600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>72300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>49100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>87200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>100500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,8 +2729,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2719,86 +2770,89 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>14800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>631600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1056500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>586400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>801900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>105900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>225500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>186600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>787500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-150600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-176600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-73500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-167400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-22100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-84700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>94500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>212000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>225300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>416800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>252900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>181000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>226700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>124400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2835,86 +2889,89 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>23600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>648000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1069700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>524900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>669900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>96700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>204900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>180700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>761500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-128000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-154900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-52700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-151500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-78200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>76800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>215600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>226900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>405100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>235900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>171800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>217300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>130700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3067,12 +3127,12 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3">
         <v>3400</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
@@ -3080,37 +3140,37 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-1800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>38300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-37700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-230600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>1600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-28600</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3443,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,86 +3484,89 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>-54100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-72400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>96300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-221000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-83700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>62000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-54000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-65600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-184400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>152000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-62700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>426500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-52700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>170700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>51800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-20800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>51000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>27200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>30000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>38200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>77500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>102800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>3800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3531,86 +3603,89 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>27000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>648000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1069700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>524900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>670300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>94900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>243100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>143000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>531000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-126400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-183500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-52700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-151500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-78200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>76800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>215600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>226900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>405100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>235900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>171800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>217300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>130700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3800,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3763,207 +3841,213 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>27000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>648000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1069700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>524900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>670300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>94900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>243100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>143000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>531000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-126400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-183500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-52700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-151500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-78200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>76800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>215600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>226900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>405100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>235900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>171800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>217300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>130700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,279 +4131,286 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1595600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1472100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1859300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1800900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1324600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1792500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1772300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1811800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2427700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1791500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2094600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2951600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2802900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2445300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2324700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1935400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1767600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1895000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1411900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1489200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1826900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1772200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1558500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1231800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1359800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1224500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>690500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>676400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>700300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>581300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>925500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>991000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>792500</v>
+      </c>
+      <c r="E42" s="3">
         <v>814200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>301600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>279800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>138700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>373000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>352800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>458700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>165300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>197000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>108000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>257700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>498400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>699800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>799200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1217100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>740600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>401300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>439800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>463900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>472400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>602900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>587200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>279600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>177500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>196100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>180500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>183700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>200400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>195800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>216300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>200600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>244200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>259400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>600500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>580000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>624900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2572600</v>
+      </c>
+      <c r="E43" s="3">
         <v>2796700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2788000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2960500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2509500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2735900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2692200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2674800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2505200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2474300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2571100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2710400</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4344,213 +4436,219 @@
         <v>0</v>
       </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
         <v>2053100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1916200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2485800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2098400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2769100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2681000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2665200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2340300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2222700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2757500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2723100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2626600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2595900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2481100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2481200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2365500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2335200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2509700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2592500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2687500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2888800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2824500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2969600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2790300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2308200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1783900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1547700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1346600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1420300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2019000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1953900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2064700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2275600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2303900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2609300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2626900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2830700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2987800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2446600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>364500</v>
+      </c>
+      <c r="E45" s="3">
         <v>115200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>147000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>122500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>202700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>122300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>89300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>506100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>645900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>161800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>253900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>124600</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4575,24 +4673,24 @@
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4608,8 +4706,8 @@
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI45" s="3">
-        <v>0</v>
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ45" s="3">
         <v>0</v>
@@ -4617,481 +4715,496 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
-      <c r="AL45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM45" s="3">
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN45" s="3">
         <v>100</v>
       </c>
-      <c r="AN45" s="3" t="s">
+      <c r="AO45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8082800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7921200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7722400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7759500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6656600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7504900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7272100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7786500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8253900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7217200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7715200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8933000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8381600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8805000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8680700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7834500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6161000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5709900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4778100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5039700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6220500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6382300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6126600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6272800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5939600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6848100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6712900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6370100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6204900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5565400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2330900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2309300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2269100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2252000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2348000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2303200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2333900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2078600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2196300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2309800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2264800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2157400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1995700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2139000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1902400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1669800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1661200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1639100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1620400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1709100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1790700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1220500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1278300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1402500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1272900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1421300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1264500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1284800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1305300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1134900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7750700</v>
+      </c>
+      <c r="E48" s="3">
         <v>7655600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7516500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7156500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6860100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7159600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6986200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7140500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7394300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6973400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6808700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6484500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5892200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5899500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5589200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5176500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5139600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5300600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5068900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5346400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6654500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6955000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7139400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7892200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8217200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8909600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8463300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8251000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8390300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6777500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>759700</v>
+      </c>
+      <c r="E49" s="3">
         <v>772500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>780100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>753800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>742500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>791400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>785000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>807100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>833000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1014900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>953000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>940600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>872700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>927900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>889200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>821900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>832600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>862900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>827400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>872700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>969200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1003200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1039500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1281300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1272900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1407600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1328000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1260400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1291000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1094100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>628400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>645800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>729800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>716500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1442000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1912400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1807500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1855000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1272400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1875600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1880000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1866500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1380800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1731900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1709700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1694600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1535900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1792600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1727800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2033600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1719200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1577300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2964500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3126800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1394500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1241200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1246600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1307400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1493200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1516400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1538900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1473100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1415700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1311300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20662900</v>
+      </c>
+      <c r="E54" s="3">
         <v>20571000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20095600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19776800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18253100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19634700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19257200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19679200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20360500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19247100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19451400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20210100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18678000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19564000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18789300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17536300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15513700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15089800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15259200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16094600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17029400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16802100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16830500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>18156200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18195900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20103100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19307700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18639300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>18607200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15883200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +5883,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1892800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2507000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2523000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2560900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1733100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2481500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2471400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2450600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1842200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2331100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2381600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2457200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2292100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2525800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2765700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2298400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1901800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1909600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1642500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1732400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1962600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1809700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1691000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2183800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2068800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2373000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2429800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2507100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2299400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2036400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>808400</v>
+      </c>
+      <c r="E58" s="3">
         <v>829100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>762100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1250000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1021100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1323400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1524800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>754300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>701300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>540500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>491700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>564000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>634400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1048500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>739500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>646800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>393700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>393500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>442200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>466400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>491800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>700500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>718600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>782800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>681500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>731100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>945500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1009000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1057500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>675900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>508300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>571600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>954700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>433200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>429200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>404800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>975300</v>
+      </c>
+      <c r="E59" s="3">
         <v>809900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>734600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>892200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>701400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>899800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>803500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>755900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>775900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1040300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>894900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1026900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1099000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1102300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1017300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1146500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>663900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>488300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>379600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>400400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>554400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>370700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>376900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>483300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>535900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>492900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>426400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>529000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>684000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>603300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>509000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>526400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>410100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>337100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>411300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>458100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4676500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4146000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4019700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4703100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4349200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4704600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4799600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3960800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4342400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3911900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3768200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4048000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4025600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4676600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4522500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4091700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2959400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2791300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2464300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2599200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3008800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2880900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2786600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3450000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3286200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3597000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3801800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4045200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4040900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3315500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2819700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2875400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2949500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2283400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2037400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2266300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2145800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2862000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2857700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2807800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2775900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2831300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2447800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1966500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1997200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1927300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2398100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2310300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2225300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2347100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2569900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2620900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2694100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2156700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2087200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2405400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2153000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1195400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1054000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>806700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>959300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>948900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>356300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>368600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>415900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>550400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1119900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1177200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1142000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1088100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1127800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1304200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1225400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1231800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1165300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1052300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1113000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1063200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2067400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2223100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2306000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2416100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2541500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2318000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3260900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3439400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3429000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3510900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3361000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3719000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3516400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3912800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3455400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3278400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3547300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2811300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10039100</v>
+      </c>
+      <c r="E66" s="3">
         <v>9652600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9558300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9394400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8795000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9615900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9512700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9361100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9790500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9143700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9017800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9277000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9043200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9430600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9365200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8947600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8220700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7761700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8228700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8679200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9335600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9322800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9168900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9726700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9348900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10441200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9925000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9051500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8925000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7391100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5943400</v>
+      </c>
+      <c r="E72" s="3">
         <v>6235200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5939300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6126400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5259200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5487000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5347600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5727400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6003500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5895800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5914400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6830300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6616700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6613600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6265000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6022700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4972300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4877400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5029300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5304700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5389100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5010800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5033300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5159600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5837800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6405600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6299500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6466900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6443600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5915000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9904400</v>
+      </c>
+      <c r="E76" s="3">
         <v>10178200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9811900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9735200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8930700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9413300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9238400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9741300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9918700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9664100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9970100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10380800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9634900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10133300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9424100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8588600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7292900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7328000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7030500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7415500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7693800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7479300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7661600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8429500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8847000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9661900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9382700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9587900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9682200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8492100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8304,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8275,86 +8469,89 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>27000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>648000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1069700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>524900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>670300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>94900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>243100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>143000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>531000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-126400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-183500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-52700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-151500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-78200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>76800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>215600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>226900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>405100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>235900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>171800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>217300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>130700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>187500</v>
+      </c>
+      <c r="E83" s="3">
         <v>232800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>234400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>228200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>199600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>218200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>218300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>209300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>196700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>219400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>230700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>240400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>206700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>205700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>184700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>226800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>197700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>178000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>186100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>415700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>211200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>400700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>222800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>337000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>269100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>243500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>237500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>193900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>189400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>193300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>207100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>228100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>168000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>160800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>166700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>197300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>792900</v>
+      </c>
+      <c r="E89" s="3">
         <v>370200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>755200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>378300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>581200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>442100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>392100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>327200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>477100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>943200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>354100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>790800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>569100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1432200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-17100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>791900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>615000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-54000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>563900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>457800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>221800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>138000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>628700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>420200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>300600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>88200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>106500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>263300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>155300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>215800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>740900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>341600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>501400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>82400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>523700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-402700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-216400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-262700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-257000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-384700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-272300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-304000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-284200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-426900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-324300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-251700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-182900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-127700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-116400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-320200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-237200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-258000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-184600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-284000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-183700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-545200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-695800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-268700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-260600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-374000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-313900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>27300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-522000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-528600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-706400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-443400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-297600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-398200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-393500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-45700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-154100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-265300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-138800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>85700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-128800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>12700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-131700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-456900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-194500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-324000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-234000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-310700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-182800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-292200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-154800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>220100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,74 +9987,75 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>439400</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>470600</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>1072900</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>-11200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-281500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-24300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-241200</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-272200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -9830,49 +10063,52 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-295800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-113600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-85000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-528300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>343600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-569600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-135100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-445800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>838600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-42400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1340300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-118000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-151900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>38200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-250200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-49300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-493200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-73900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>669000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-107400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-208300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>531200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>115200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>45700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>22200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>101800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>602000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>26000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E101" s="3">
         <v>5900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-28700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>60200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-75000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-42300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>55000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>82400</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3">
         <v>67800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>82100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>29800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-42800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>69600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>76900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>23900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>13900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-19000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>32500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-28500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-33400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-95400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>58500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>21100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>44000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>31000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>9000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>30300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>137100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-411100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>370300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-336800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-55200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-461000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>562200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-313900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-785500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>102100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>371700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>127200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>317400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-161200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>388600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-127500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>483000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-260500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>14800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>213700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>326700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>188700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>519300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>11800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-96000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>119100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>36500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>10500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-156300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,173 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -862,86 +866,89 @@
       <c r="O8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="3">
         <v>4144800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4960800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6146300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4263500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4367500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3452900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3250600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3169900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1249900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2787400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2567200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3202000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3928000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4515500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4529900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4254800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4330700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,86 +988,89 @@
       <c r="O9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>2713700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3246800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3512800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2667000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2333100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2229300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1995300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1897500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>625800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1676100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1603700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1894400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2471300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2899500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2997100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2845600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2839000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2625700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1100,86 +1110,89 @@
       <c r="O10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1431100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1714000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2633500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1596500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2034400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1223600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1255300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1272400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>624100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1111300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>963600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1307600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1456800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1616100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1532800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1409100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1491700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1442300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>929900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>969000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1500,48 +1520,48 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>27000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4600</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>27700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>6500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>185300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>100900</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1557,11 +1577,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
@@ -1578,8 +1598,11 @@
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1619,86 +1642,89 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3">
         <v>213500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>202000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>205600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>184700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>199100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>196400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>177300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>174000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>88100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>173300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>184400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>192100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>236000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>269100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>243400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>237500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>193900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>189400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>193400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>207100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>228100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>167900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>160800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>166700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>197200</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,8 +1763,9 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1778,86 +1805,89 @@
       <c r="O17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>4012700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4235300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4683700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3694400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3418800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3214700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2965200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2948300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>535800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2595600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2728100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2976300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3972200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4488800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4454100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4252500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4310600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3857600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1897,86 +1927,89 @@
       <c r="O18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>132100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>725500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1462600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>569100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>948700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>238300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>285400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>221500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>714100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>191800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-160900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>225700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-44200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>26700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>75900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>210400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>305500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>358100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>522300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>269000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>341100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>297200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>242200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2051,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,86 +2093,89 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>54100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>72400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-96300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>221000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>83700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-62000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>54000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>65600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>184400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-152000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>62700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-426500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>52700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-170700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-51800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>20800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-51000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-27200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>60900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>27100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2178,86 +2215,89 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>426600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1004500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1571900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>974800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1259200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>374000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>517300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>473200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1085900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>220600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>271500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>345500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>125200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>267600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>260600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>163000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>372600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>468800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>527000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>673000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>497900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>399100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>491000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>435600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2297,86 +2337,89 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>28600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>25400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>28000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>26200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>22100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>27000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>20200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>30300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>16100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>15100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>12400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>4700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>8200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>10400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>13400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2416,86 +2459,89 @@
       <c r="O23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>157600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>772400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1338300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>769700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1009300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>152400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>318800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>263600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>872200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>13400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-121600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-222900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-169300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-61300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>167200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>260400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>306600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>432500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>325100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>230100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>313900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>224900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2535,86 +2581,89 @@
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>142800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>140800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>281800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>183400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>207400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>46500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>93300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>77000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>84700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>24500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>29100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-46300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>55000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>21200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>17000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>23500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>72600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>48400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>81300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>15600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>72300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>49100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>87200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>100500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,8 +2781,11 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2773,86 +2825,89 @@
       <c r="O26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>14800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>631600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1056500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>586400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>801900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>105900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>225500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>186600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>787500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-150600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-176600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-73500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-167400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-22100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-84700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>94500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>212000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>225300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>416800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>252900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>181000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>226700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>124400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2892,86 +2947,89 @@
       <c r="O27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>23600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>648000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1069700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>524900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>669900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>96700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>204900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>180700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>761500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-128000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-154900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-52700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-151500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-78200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>76800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>215600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>405100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>235900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>171800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>217300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>130700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3130,12 +3191,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
         <v>3400</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
@@ -3143,37 +3204,37 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-1800</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>38300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-37700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-230600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>1600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-28600</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3513,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,86 +3557,89 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-72400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>96300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-221000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-83700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>62000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-54000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-65600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-184400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>152000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-62700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>426500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-52700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>170700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>51800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-20800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>51000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>27200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>30000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>38200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>77500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>102800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3606,86 +3679,89 @@
       <c r="O33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>27000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>648000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1069700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>524900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>670300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>94900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>243100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>143000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>531000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-22600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-126400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-183500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-52700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-151500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-78200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>76800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>215600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>405100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>235900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>171800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>217300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>130700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,8 +3879,11 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3844,210 +3923,216 @@
       <c r="O35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>27000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>648000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1069700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>524900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>670300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>94900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>243100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>143000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>531000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-22600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-126400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-183500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-52700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-151500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-78200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>76800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>215600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>405100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>235900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>171800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>217300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>130700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,288 +4218,295 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1155200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1595600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1472100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1859300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1800900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1324600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1792500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1772300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1811800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2427700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1791500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2094600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2951600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2802900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2445300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2324700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1935400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1767600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1895000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1411900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1489200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1826900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1772200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1558500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1231800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1359800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1224500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>690500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>676400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>700300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>581300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>925500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>991000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>966500</v>
+      </c>
+      <c r="E42" s="3">
         <v>792500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>814200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>301600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>279800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>138700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>373000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>352800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>458700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>165300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>197000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>108000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>257700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>498400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>699800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>799200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1217100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>740600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>401300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>439800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>463900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>472400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>602900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>587200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>279600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>177500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>196100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>180500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>183700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>200400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>195800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>216300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>200600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>244200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>259400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>600500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>580000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>624900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3222400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2572600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2796700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2788000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2960500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2509500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2735900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2692200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2674800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2505200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2474300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2571100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2710400</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4439,219 +4532,225 @@
         <v>0</v>
       </c>
       <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>2053100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1916200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2485800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2098400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2769100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2681000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2665200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2340300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2222700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2845400</v>
+      </c>
+      <c r="E44" s="3">
         <v>2757500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2723100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2626600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2595900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2481100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2481200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2365500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2335200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2509700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2592500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2687500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2888800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2824500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2969600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2790300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2308200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1783900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1547700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1346600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1420300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2019000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1953900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2064700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2275600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2303900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2609300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2626900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2830700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2987800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2446600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E45" s="3">
         <v>364500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>115200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>147000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>122500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>202700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>122300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>89300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>506100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>645900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>161800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>253900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>124600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4676,24 +4775,24 @@
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4709,8 +4808,8 @@
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ45" s="3">
-        <v>0</v>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK45" s="3">
         <v>0</v>
@@ -4718,493 +4817,508 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
-      <c r="AM45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN45" s="3">
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO45" s="3">
         <v>100</v>
       </c>
-      <c r="AO45" s="3" t="s">
+      <c r="AP45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8359600</v>
+      </c>
+      <c r="E46" s="3">
         <v>8082800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7921200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7722400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7759500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6656600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7504900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7272100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7786500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8253900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7217200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7715200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8933000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8381600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8805000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8680700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7834500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6161000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5709900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4778100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5039700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6220500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6382300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6126600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6272800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5939600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6848100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6712900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6370100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6204900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5565400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2223400</v>
+      </c>
+      <c r="E47" s="3">
         <v>2330900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2309300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2269100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2252000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2348000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2303200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2333900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2078600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2196300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2309800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2264800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2157400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1995700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2139000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1902400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1669800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1661200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1639100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1620400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1709100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1790700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1220500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1278300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1402500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1272900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1421300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1264500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1284800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1305300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1134900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7897700</v>
+      </c>
+      <c r="E48" s="3">
         <v>7750700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7655600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7516500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7156500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6860100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7159600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6986200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7140500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7394300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6973400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6808700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6484500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5892200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5899500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5589200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5176500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5139600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5300600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5068900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5346400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6654500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6955000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7139400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7892200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8217200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8909600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8463300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8251000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8390300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6777500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>748900</v>
+      </c>
+      <c r="E49" s="3">
         <v>759700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>772500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>780100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>753800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>742500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>791400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>785000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>807100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>833000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1014900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>953000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>940600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>872700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>927900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>889200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>821900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>832600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>862900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>827400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>872700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>969200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1003200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1039500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1281300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1272900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1407600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1328000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1260400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1291000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1094100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>628400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>645800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>729800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>716500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2017400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1442000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1912400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1807500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1855000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1272400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1875600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1880000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1866500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1380800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1731900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1709700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1694600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1535900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1792600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1727800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2033600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1719200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1577300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2964500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3126800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1394500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1241200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1246600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1307400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1493200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1516400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1538900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1473100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1415700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1311300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21247000</v>
+      </c>
+      <c r="E54" s="3">
         <v>20662900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20571000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20095600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19776800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18253100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19634700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19257200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19679200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20360500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19247100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19451400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20210100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18678000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19564000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18789300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17536300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15513700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15089800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15259200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16094600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17029400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16802100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16830500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18156200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18195900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>20103100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19307700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>18639300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18607200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15883200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,722 +6014,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2655700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1892800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2507000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2523000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2560900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1733100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2481500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2471400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2450600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1842200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2331100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2381600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2457200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2292100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2525800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2765700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2298400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1901800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1909600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1642500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1732400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1962600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1809700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1691000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2183800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2068800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2373000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2429800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2507100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2299400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2036400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>523900</v>
+      </c>
+      <c r="E58" s="3">
         <v>808400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>829100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>762100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1250000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1021100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1323400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1524800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>754300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>701300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>540500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>491700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>564000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>634400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1048500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>739500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>646800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>393700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>393500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>442200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>466400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>491800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>700500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>718600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>782800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>681500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>731100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>945500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1009000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1057500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>675900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>508300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>571600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>954700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>433200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>429200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>404800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1330800</v>
+      </c>
+      <c r="E59" s="3">
         <v>975300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>809900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>734600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>892200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>701400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>899800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>803500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>755900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>775900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1040300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>894900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1026900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1099000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1102300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1017300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1146500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>663900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>488300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>379600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>400400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>554400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>370700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>376900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>483300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>535900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>492900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>426400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>529000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>684000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>603300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>509000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>526400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>410100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>337100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>411300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>458100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4510400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4676500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4146000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4019700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4703100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4349200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4704600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4799600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3960800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4342400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3911900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3768200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4048000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4025600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4676600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4522500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4091700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2959400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2791300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2464300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2599200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3008800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2880900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2786600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3450000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3286200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3597000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3801800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4045200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4040900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3315500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2941900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2819700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2875400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2949500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2283400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2037400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2266300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2145800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2862000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2857700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2807800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2775900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2831300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2447800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1966500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1997200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1927300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2398100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2310300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2225300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2347100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2569900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2620900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2694100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2156700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2087200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2405400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2153000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1195400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1054000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>806700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>959300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>948900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>356300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>368600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>415900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>550400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1098600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1119900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1177200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1142000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1088100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1127800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1304200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1225400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1231800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1165300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1052300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1113000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1063200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2067400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2223100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2306000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2416100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2541500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2318000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3260900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3439400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3429000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3510900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3361000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3719000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3516400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3912800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3455400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3278400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3547300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2811300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9952000</v>
+      </c>
+      <c r="E66" s="3">
         <v>10039100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9652600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9558300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9394400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8795000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9615900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9512700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9361100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9790500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9143700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9017800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9277000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9043200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9430600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9365200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8947600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8220700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7761700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8228700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8679200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9335600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9322800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9168900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9726700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9348900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10441200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9925000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9051500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8925000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7391100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6586700</v>
+      </c>
+      <c r="E72" s="3">
         <v>5943400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6235200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5939300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6126400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5259200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5487000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5347600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5727400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6003500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5895800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5914400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6830300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6616700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6613600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6265000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6022700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4972300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4877400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5029300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5304700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5389100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5010800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5033300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5159600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5837800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6405600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6299500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6466900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6443600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5915000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10525400</v>
+      </c>
+      <c r="E76" s="3">
         <v>9904400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10178200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9811900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9735200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8930700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9413300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9238400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9741300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9918700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9664100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9970100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10380800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9634900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10133300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9424100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8588600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7292900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7328000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7030500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7415500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7693800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7479300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7661600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8429500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8847000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9661900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9382700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9587900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9682200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8492100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,132 +8496,138 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8472,86 +8667,89 @@
       <c r="O81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>27000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>648000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1069700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>524900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>670300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>94900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>243100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>143000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>531000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-22600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-126400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-183500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-52700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-151500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-78200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>76800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>215600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>405100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>235900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>171800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>217300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>130700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E83" s="3">
         <v>187500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>232800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>234400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>228200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>199600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>218200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>218300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>209300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>196700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>219400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>230700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>240400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>206700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>205700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>184700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>226800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>197700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>178000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>186100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>415700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>211200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>400700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>222800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>337000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>269100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>243500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>237500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>193900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>189400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>193300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>207100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>228100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>168000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>160800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>166700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>197300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-194200</v>
+      </c>
+      <c r="E89" s="3">
         <v>792900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>370200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>755200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>378300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>581200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>442100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>392100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>327200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>477100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>943200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>354100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>790800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>569100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1432200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>791900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>615000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-54000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>563900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>457800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>221800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>138000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>628700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>420200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>300600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>88200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>106500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>263300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>155300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>215800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>740900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>341600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>501400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>82400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>523700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-282600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-402700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-216400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-262700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-257000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-384700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-272300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-304000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-284200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-426900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-324300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-251700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-182900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-127700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-116400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-320200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-237200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-258000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-184600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-284000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-183700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-545200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-695800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-268700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-260600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-374000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-313900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>27300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-522000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-528600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-706400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-443400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-297600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-398200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-393500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-45700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-154100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-265300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-138800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>85700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-128800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>12700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-131700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-456900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-194500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-324000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-234000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-310700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-182800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-292200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-154800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>220100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,77 +10221,78 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>13500</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>439400</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>470600</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3">
         <v>1072900</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-281500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-24300</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-241200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-272200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -10066,49 +10300,52 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-295800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-192700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-113600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-85000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-528300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>343600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-569600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-135100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-445800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>838600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-42400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1340300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>21900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-118000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-151900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>38200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-250200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-49300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-493200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-73900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>669000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-107400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-208300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>531200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>115200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>45700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>22200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>101800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>602000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>26000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-91100</v>
+      </c>
+      <c r="E101" s="3">
         <v>25600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-28700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>60200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-75000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-42300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>55000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>82400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>67800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>82100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>29800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>69600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>76900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>23900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>13900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-19000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>32500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-28500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-33400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-95400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>58500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>21100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>44000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>31000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>9000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>30300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-496300</v>
+      </c>
+      <c r="E102" s="3">
         <v>137100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-411100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>370300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-336800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-55200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-461000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>562200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-313900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-785500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>102100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>371700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>127200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>317400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-161200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>388600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-127500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>483000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-260500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>213700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>326700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>188700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>519300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>11800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-96000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>119100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>36500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>10500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-156300</v>
       </c>
     </row>
